--- a/AAII_Financials/Yearly/NTES_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NTES_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
   <si>
     <t>NTES</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>13324100</v>
+        <v>14384100</v>
       </c>
       <c r="E8" s="3">
-        <v>12096600</v>
+        <v>13414800</v>
       </c>
       <c r="F8" s="3">
-        <v>10172000</v>
+        <v>12179000</v>
       </c>
       <c r="G8" s="3">
-        <v>8180000</v>
+        <v>10241200</v>
       </c>
       <c r="H8" s="3">
-        <v>7066700</v>
+        <v>8235700</v>
       </c>
       <c r="I8" s="3">
-        <v>6135900</v>
+        <v>7114800</v>
       </c>
       <c r="J8" s="3">
+        <v>6177700</v>
+      </c>
+      <c r="K8" s="3">
         <v>4693900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3018900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1847800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1405000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1176700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1082000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6038200</v>
+        <v>5617100</v>
       </c>
       <c r="E9" s="3">
-        <v>5610900</v>
+        <v>6079300</v>
       </c>
       <c r="F9" s="3">
-        <v>4789100</v>
+        <v>5649100</v>
       </c>
       <c r="G9" s="3">
-        <v>3822900</v>
+        <v>4821700</v>
       </c>
       <c r="H9" s="3">
-        <v>3290800</v>
+        <v>3848900</v>
       </c>
       <c r="I9" s="3">
-        <v>2678000</v>
+        <v>3313200</v>
       </c>
       <c r="J9" s="3">
+        <v>2696200</v>
+      </c>
+      <c r="K9" s="3">
         <v>4052500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2470500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>514500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>378700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>369900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>352100</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>7285900</v>
+        <v>8767100</v>
       </c>
       <c r="E10" s="3">
-        <v>6485700</v>
+        <v>7335500</v>
       </c>
       <c r="F10" s="3">
-        <v>5382800</v>
+        <v>6529900</v>
       </c>
       <c r="G10" s="3">
-        <v>4357200</v>
+        <v>5419500</v>
       </c>
       <c r="H10" s="3">
-        <v>3776000</v>
+        <v>4386800</v>
       </c>
       <c r="I10" s="3">
-        <v>3457900</v>
+        <v>3801700</v>
       </c>
       <c r="J10" s="3">
+        <v>3481500</v>
+      </c>
+      <c r="K10" s="3">
         <v>641400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>548400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1333300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1026300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>806800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>729900</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>2076600</v>
+        <v>2291700</v>
       </c>
       <c r="E12" s="3">
-        <v>1943600</v>
+        <v>2090700</v>
       </c>
       <c r="F12" s="3">
-        <v>1431800</v>
+        <v>1956800</v>
       </c>
       <c r="G12" s="3">
-        <v>1161700</v>
+        <v>1441600</v>
       </c>
       <c r="H12" s="3">
-        <v>1018800</v>
+        <v>1169600</v>
       </c>
       <c r="I12" s="3">
-        <v>574600</v>
+        <v>1025800</v>
       </c>
       <c r="J12" s="3">
+        <v>578600</v>
+      </c>
+      <c r="K12" s="3">
         <v>823900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>595900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>208800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>140800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>103100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>69100</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -944,23 +960,26 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="3">
         <v>7700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7700</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>17</v>
@@ -977,8 +996,8 @@
       <c r="L14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -986,9 +1005,12 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>10621500</v>
+        <v>10532000</v>
       </c>
       <c r="E17" s="3">
-        <v>9832400</v>
+        <v>10693800</v>
       </c>
       <c r="F17" s="3">
-        <v>8172200</v>
+        <v>9899400</v>
       </c>
       <c r="G17" s="3">
-        <v>6275800</v>
+        <v>8227800</v>
       </c>
       <c r="H17" s="3">
-        <v>5689100</v>
+        <v>6318500</v>
       </c>
       <c r="I17" s="3">
-        <v>4341600</v>
+        <v>5727800</v>
       </c>
       <c r="J17" s="3">
+        <v>4371100</v>
+      </c>
+      <c r="K17" s="3">
         <v>2902700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1979200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1096100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>740000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>644100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>588800</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>2702600</v>
+        <v>3852100</v>
       </c>
       <c r="E18" s="3">
-        <v>2264200</v>
+        <v>2721000</v>
       </c>
       <c r="F18" s="3">
-        <v>1999800</v>
+        <v>2279600</v>
       </c>
       <c r="G18" s="3">
-        <v>1904200</v>
+        <v>2013400</v>
       </c>
       <c r="H18" s="3">
-        <v>1377700</v>
+        <v>1917200</v>
       </c>
       <c r="I18" s="3">
-        <v>1794300</v>
+        <v>1387100</v>
       </c>
       <c r="J18" s="3">
+        <v>1806600</v>
+      </c>
+      <c r="K18" s="3">
         <v>1791300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1039700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>751700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>665000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>532500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>493200</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>735600</v>
+        <v>882500</v>
       </c>
       <c r="E20" s="3">
-        <v>676300</v>
+        <v>740600</v>
       </c>
       <c r="F20" s="3">
-        <v>157000</v>
+        <v>680900</v>
       </c>
       <c r="G20" s="3">
-        <v>415900</v>
+        <v>158100</v>
       </c>
       <c r="H20" s="3">
-        <v>195400</v>
+        <v>418700</v>
       </c>
       <c r="I20" s="3">
-        <v>129300</v>
+        <v>196800</v>
       </c>
       <c r="J20" s="3">
+        <v>130200</v>
+      </c>
+      <c r="K20" s="3">
         <v>179100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>119200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>112500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>97100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>81300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>43400</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>3832700</v>
+        <v>5159800</v>
       </c>
       <c r="E21" s="3">
-        <v>3392600</v>
+        <v>3859400</v>
       </c>
       <c r="F21" s="3">
-        <v>2634000</v>
+        <v>3416400</v>
       </c>
       <c r="G21" s="3">
-        <v>2680800</v>
+        <v>2652700</v>
       </c>
       <c r="H21" s="3">
-        <v>1860600</v>
+        <v>2699600</v>
       </c>
       <c r="I21" s="3">
-        <v>2034300</v>
+        <v>1873700</v>
       </c>
       <c r="J21" s="3">
+        <v>2048400</v>
+      </c>
+      <c r="K21" s="3">
         <v>2015600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1184100</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O21" s="3">
         <v>647300</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3">
-        <v>89800</v>
+      <c r="D22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E22" s="3">
-        <v>26400</v>
+        <v>90400</v>
       </c>
       <c r="F22" s="3">
-        <v>34200</v>
+        <v>26600</v>
       </c>
       <c r="G22" s="3">
-        <v>57900</v>
+        <v>34400</v>
       </c>
       <c r="H22" s="3">
-        <v>43600</v>
+        <v>58300</v>
       </c>
       <c r="I22" s="3">
-        <v>12700</v>
+        <v>43900</v>
       </c>
       <c r="J22" s="3">
+        <v>12800</v>
+      </c>
+      <c r="K22" s="3">
         <v>4400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1900</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3348500</v>
+        <v>4734600</v>
       </c>
       <c r="E23" s="3">
-        <v>2914100</v>
+        <v>3371300</v>
       </c>
       <c r="F23" s="3">
-        <v>2122600</v>
+        <v>2933900</v>
       </c>
       <c r="G23" s="3">
-        <v>2262200</v>
+        <v>2137000</v>
       </c>
       <c r="H23" s="3">
-        <v>1529500</v>
+        <v>2277600</v>
       </c>
       <c r="I23" s="3">
-        <v>1911000</v>
+        <v>1539900</v>
       </c>
       <c r="J23" s="3">
+        <v>1924000</v>
+      </c>
+      <c r="K23" s="3">
         <v>1965900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1156200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>861100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>760200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>613800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>536600</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>694800</v>
+        <v>653400</v>
       </c>
       <c r="E24" s="3">
-        <v>570000</v>
+        <v>699500</v>
       </c>
       <c r="F24" s="3">
-        <v>420000</v>
+        <v>573900</v>
       </c>
       <c r="G24" s="3">
-        <v>402500</v>
+        <v>422900</v>
       </c>
       <c r="H24" s="3">
-        <v>339800</v>
+        <v>405200</v>
       </c>
       <c r="I24" s="3">
-        <v>297700</v>
+        <v>342100</v>
       </c>
       <c r="J24" s="3">
+        <v>299700</v>
+      </c>
+      <c r="K24" s="3">
         <v>290300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>175500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>104600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>81100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>99200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>58300</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2653700</v>
+        <v>4081200</v>
       </c>
       <c r="E26" s="3">
-        <v>2344100</v>
+        <v>2671700</v>
       </c>
       <c r="F26" s="3">
-        <v>1702600</v>
+        <v>2360000</v>
       </c>
       <c r="G26" s="3">
-        <v>1859700</v>
+        <v>1714100</v>
       </c>
       <c r="H26" s="3">
-        <v>1189700</v>
+        <v>1872400</v>
       </c>
       <c r="I26" s="3">
-        <v>1613300</v>
+        <v>1197800</v>
       </c>
       <c r="J26" s="3">
+        <v>1624300</v>
+      </c>
+      <c r="K26" s="3">
         <v>1675700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>980700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>756600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>679100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>514600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>478300</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2721900</v>
+        <v>4089500</v>
       </c>
       <c r="E27" s="3">
-        <v>2327600</v>
+        <v>2740500</v>
       </c>
       <c r="F27" s="3">
-        <v>1665600</v>
+        <v>2343400</v>
       </c>
       <c r="G27" s="3">
-        <v>1833000</v>
+        <v>1677000</v>
       </c>
       <c r="H27" s="3">
-        <v>1144800</v>
+        <v>1845500</v>
       </c>
       <c r="I27" s="3">
-        <v>1593800</v>
+        <v>1152600</v>
       </c>
       <c r="J27" s="3">
+        <v>1604600</v>
+      </c>
+      <c r="K27" s="3">
         <v>1649600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>966500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>750400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>678900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>521900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>480000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,51 +1580,57 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>86300</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>86900</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>1099500</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-295300</v>
+        <v>1106900</v>
       </c>
       <c r="I29" s="3">
-        <v>-115200</v>
+        <v>-297300</v>
       </c>
       <c r="J29" s="3">
+        <v>-116000</v>
+      </c>
+      <c r="K29" s="3">
         <v>-47300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-29000</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-735600</v>
+        <v>-882500</v>
       </c>
       <c r="E32" s="3">
-        <v>-676300</v>
+        <v>-740600</v>
       </c>
       <c r="F32" s="3">
-        <v>-157000</v>
+        <v>-680900</v>
       </c>
       <c r="G32" s="3">
-        <v>-415900</v>
+        <v>-158100</v>
       </c>
       <c r="H32" s="3">
-        <v>-195400</v>
+        <v>-418700</v>
       </c>
       <c r="I32" s="3">
-        <v>-129300</v>
+        <v>-196800</v>
       </c>
       <c r="J32" s="3">
+        <v>-130200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-179100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-119200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-112500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-97100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-81300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-43400</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2808200</v>
+        <v>4089500</v>
       </c>
       <c r="E33" s="3">
-        <v>2327600</v>
+        <v>2827300</v>
       </c>
       <c r="F33" s="3">
-        <v>1665600</v>
+        <v>2343400</v>
       </c>
       <c r="G33" s="3">
-        <v>2932500</v>
+        <v>1677000</v>
       </c>
       <c r="H33" s="3">
-        <v>849500</v>
+        <v>2952400</v>
       </c>
       <c r="I33" s="3">
-        <v>1478600</v>
+        <v>855300</v>
       </c>
       <c r="J33" s="3">
+        <v>1488600</v>
+      </c>
+      <c r="K33" s="3">
         <v>1602400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>937500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>750400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>678900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>521900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>480000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2808200</v>
+        <v>4089500</v>
       </c>
       <c r="E35" s="3">
-        <v>2327600</v>
+        <v>2827300</v>
       </c>
       <c r="F35" s="3">
-        <v>1665600</v>
+        <v>2343400</v>
       </c>
       <c r="G35" s="3">
-        <v>2932500</v>
+        <v>1677000</v>
       </c>
       <c r="H35" s="3">
-        <v>849500</v>
+        <v>2952400</v>
       </c>
       <c r="I35" s="3">
-        <v>1478600</v>
+        <v>855300</v>
       </c>
       <c r="J35" s="3">
+        <v>1488600</v>
+      </c>
+      <c r="K35" s="3">
         <v>1602400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>937500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>750400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>678900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>521900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>480000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,166 +1986,176 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3436700</v>
+        <v>2979000</v>
       </c>
       <c r="E41" s="3">
-        <v>2001900</v>
+        <v>3460100</v>
       </c>
       <c r="F41" s="3">
-        <v>1258900</v>
+        <v>2015500</v>
       </c>
       <c r="G41" s="3">
-        <v>448300</v>
+        <v>1267500</v>
       </c>
       <c r="H41" s="3">
-        <v>688800</v>
+        <v>451300</v>
       </c>
       <c r="I41" s="3">
-        <v>381700</v>
+        <v>693500</v>
       </c>
       <c r="J41" s="3">
+        <v>384300</v>
+      </c>
+      <c r="K41" s="3">
         <v>751100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>845200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>957800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>222800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>228200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>328700</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>12782100</v>
+        <v>14637700</v>
       </c>
       <c r="E42" s="3">
-        <v>11465700</v>
+        <v>12869100</v>
       </c>
       <c r="F42" s="3">
-        <v>11647400</v>
+        <v>11543700</v>
       </c>
       <c r="G42" s="3">
-        <v>9499900</v>
+        <v>11726700</v>
       </c>
       <c r="H42" s="3">
-        <v>6154900</v>
+        <v>9564500</v>
       </c>
       <c r="I42" s="3">
-        <v>5571000</v>
+        <v>6196800</v>
       </c>
       <c r="J42" s="3">
+        <v>5608900</v>
+      </c>
+      <c r="K42" s="3">
         <v>4272600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2729300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3093200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2677700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2033400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1587700</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>900300</v>
+        <v>892800</v>
       </c>
       <c r="E43" s="3">
-        <v>984700</v>
+        <v>906400</v>
       </c>
       <c r="F43" s="3">
-        <v>925100</v>
+        <v>991400</v>
       </c>
       <c r="G43" s="3">
-        <v>662000</v>
+        <v>931400</v>
       </c>
       <c r="H43" s="3">
-        <v>1240300</v>
+        <v>666500</v>
       </c>
       <c r="I43" s="3">
-        <v>569300</v>
+        <v>1248800</v>
       </c>
       <c r="J43" s="3">
+        <v>573200</v>
+      </c>
+      <c r="K43" s="3">
         <v>1225200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>410000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>464700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>104500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>66300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>50800</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>137200</v>
+        <v>96700</v>
       </c>
       <c r="E44" s="3">
-        <v>133200</v>
+        <v>138100</v>
       </c>
       <c r="F44" s="3">
-        <v>85800</v>
+        <v>134100</v>
       </c>
       <c r="G44" s="3">
-        <v>89800</v>
+        <v>86400</v>
       </c>
       <c r="H44" s="3">
-        <v>147100</v>
+        <v>90400</v>
       </c>
       <c r="I44" s="3">
-        <v>756000</v>
+        <v>148100</v>
       </c>
       <c r="J44" s="3">
+        <v>761100</v>
+      </c>
+      <c r="K44" s="3">
         <v>217900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>113800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>129000</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>17</v>
@@ -2068,219 +2163,237 @@
       <c r="O44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>915500</v>
+        <v>1230900</v>
       </c>
       <c r="E45" s="3">
-        <v>1034100</v>
+        <v>921700</v>
       </c>
       <c r="F45" s="3">
-        <v>972100</v>
+        <v>1041200</v>
       </c>
       <c r="G45" s="3">
-        <v>1051300</v>
+        <v>978800</v>
       </c>
       <c r="H45" s="3">
-        <v>2488200</v>
+        <v>1058500</v>
       </c>
       <c r="I45" s="3">
-        <v>1275800</v>
+        <v>2505200</v>
       </c>
       <c r="J45" s="3">
+        <v>1284500</v>
+      </c>
+      <c r="K45" s="3">
         <v>1741600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>691400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>783600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>478000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>235800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>180900</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>18171800</v>
+        <v>19837100</v>
       </c>
       <c r="E46" s="3">
-        <v>15619600</v>
+        <v>18295500</v>
       </c>
       <c r="F46" s="3">
-        <v>14889300</v>
+        <v>15726000</v>
       </c>
       <c r="G46" s="3">
-        <v>11751300</v>
+        <v>14990700</v>
       </c>
       <c r="H46" s="3">
-        <v>9488300</v>
+        <v>11831300</v>
       </c>
       <c r="I46" s="3">
-        <v>8553700</v>
+        <v>9552900</v>
       </c>
       <c r="J46" s="3">
+        <v>8612000</v>
+      </c>
+      <c r="K46" s="3">
         <v>6818900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4789700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5428400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3483000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2563800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2148100</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3211300</v>
+        <v>146000</v>
       </c>
       <c r="E47" s="3">
-        <v>3422400</v>
+        <v>3233200</v>
       </c>
       <c r="F47" s="3">
-        <v>2559900</v>
+        <v>3445700</v>
       </c>
       <c r="G47" s="3">
-        <v>1830000</v>
+        <v>2577300</v>
       </c>
       <c r="H47" s="3">
-        <v>738200</v>
+        <v>1842500</v>
       </c>
       <c r="I47" s="3">
-        <v>384500</v>
+        <v>743200</v>
       </c>
       <c r="J47" s="3">
+        <v>387100</v>
+      </c>
+      <c r="K47" s="3">
         <v>348000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>400200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>453500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>117000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>75200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>998400</v>
+        <v>1122600</v>
       </c>
       <c r="E48" s="3">
-        <v>894500</v>
+        <v>1005200</v>
       </c>
       <c r="F48" s="3">
-        <v>735800</v>
+        <v>900600</v>
       </c>
       <c r="G48" s="3">
-        <v>702200</v>
+        <v>740800</v>
       </c>
       <c r="H48" s="3">
-        <v>1387900</v>
+        <v>707000</v>
       </c>
       <c r="I48" s="3">
-        <v>520500</v>
+        <v>1397400</v>
       </c>
       <c r="J48" s="3">
+        <v>524000</v>
+      </c>
+      <c r="K48" s="3">
         <v>668200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>291200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>367700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>133200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>116900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>125900</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>591600</v>
+      <c r="D49" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E49" s="3">
-        <v>443600</v>
+        <v>595600</v>
       </c>
       <c r="F49" s="3">
-        <v>613700</v>
+        <v>446600</v>
       </c>
       <c r="G49" s="3">
-        <v>502500</v>
+        <v>617900</v>
       </c>
       <c r="H49" s="3">
-        <v>340400</v>
+        <v>505900</v>
       </c>
       <c r="I49" s="3">
-        <v>113300</v>
+        <v>342700</v>
       </c>
       <c r="J49" s="3">
+        <v>114000</v>
+      </c>
+      <c r="K49" s="3">
         <v>35100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>26600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>30100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>881800</v>
+        <v>4741600</v>
       </c>
       <c r="E52" s="3">
-        <v>835000</v>
+        <v>887800</v>
       </c>
       <c r="F52" s="3">
-        <v>791400</v>
+        <v>840700</v>
       </c>
       <c r="G52" s="3">
-        <v>696100</v>
+        <v>796800</v>
       </c>
       <c r="H52" s="3">
-        <v>1929600</v>
+        <v>700800</v>
       </c>
       <c r="I52" s="3">
-        <v>236000</v>
+        <v>1942800</v>
       </c>
       <c r="J52" s="3">
+        <v>237600</v>
+      </c>
+      <c r="K52" s="3">
         <v>818100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>221400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>213300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7900</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>23854800</v>
+        <v>25847300</v>
       </c>
       <c r="E54" s="3">
-        <v>21215200</v>
+        <v>24017200</v>
       </c>
       <c r="F54" s="3">
-        <v>19590000</v>
+        <v>21359600</v>
       </c>
       <c r="G54" s="3">
-        <v>15482100</v>
+        <v>19723400</v>
       </c>
       <c r="H54" s="3">
-        <v>12008500</v>
+        <v>15587500</v>
       </c>
       <c r="I54" s="3">
-        <v>9808000</v>
+        <v>12090300</v>
       </c>
       <c r="J54" s="3">
+        <v>9874800</v>
+      </c>
+      <c r="K54" s="3">
         <v>8013000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5729100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6493000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3750200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2766000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2292200</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,187 +2654,200 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>208100</v>
+        <v>122500</v>
       </c>
       <c r="E57" s="3">
-        <v>136000</v>
+        <v>209500</v>
       </c>
       <c r="F57" s="3">
-        <v>156600</v>
+        <v>136900</v>
       </c>
       <c r="G57" s="3">
-        <v>167400</v>
+        <v>157700</v>
       </c>
       <c r="H57" s="3">
-        <v>165900</v>
+        <v>168500</v>
       </c>
       <c r="I57" s="3">
-        <v>337300</v>
+        <v>167100</v>
       </c>
       <c r="J57" s="3">
+        <v>339600</v>
+      </c>
+      <c r="K57" s="3">
         <v>192800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>97500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>110500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>33500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>22600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>19900</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3296800</v>
+        <v>2674800</v>
       </c>
       <c r="E58" s="3">
-        <v>2672200</v>
+        <v>3319200</v>
       </c>
       <c r="F58" s="3">
-        <v>2693200</v>
+        <v>2690400</v>
       </c>
       <c r="G58" s="3">
-        <v>2323600</v>
+        <v>2711500</v>
       </c>
       <c r="H58" s="3">
-        <v>1886000</v>
+        <v>2339500</v>
       </c>
       <c r="I58" s="3">
-        <v>914600</v>
+        <v>1898800</v>
       </c>
       <c r="J58" s="3">
+        <v>920800</v>
+      </c>
+      <c r="K58" s="3">
         <v>526900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>316400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>358600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>149000</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4342100</v>
+        <v>4687900</v>
       </c>
       <c r="E59" s="3">
-        <v>4165000</v>
+        <v>4371600</v>
       </c>
       <c r="F59" s="3">
-        <v>3604500</v>
+        <v>4193400</v>
       </c>
       <c r="G59" s="3">
-        <v>2789600</v>
+        <v>3629000</v>
       </c>
       <c r="H59" s="3">
-        <v>3603500</v>
+        <v>2808500</v>
       </c>
       <c r="I59" s="3">
-        <v>2027600</v>
+        <v>3628000</v>
       </c>
       <c r="J59" s="3">
+        <v>2041400</v>
+      </c>
+      <c r="K59" s="3">
         <v>2422300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1210200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1371600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>464200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>490500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>318800</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7846900</v>
+        <v>7485200</v>
       </c>
       <c r="E60" s="3">
-        <v>6973200</v>
+        <v>7900300</v>
       </c>
       <c r="F60" s="3">
-        <v>6454300</v>
+        <v>7020700</v>
       </c>
       <c r="G60" s="3">
-        <v>5280600</v>
+        <v>6498300</v>
       </c>
       <c r="H60" s="3">
-        <v>4847900</v>
+        <v>5316500</v>
       </c>
       <c r="I60" s="3">
-        <v>3279400</v>
+        <v>4880900</v>
       </c>
       <c r="J60" s="3">
+        <v>3301700</v>
+      </c>
+      <c r="K60" s="3">
         <v>2647900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1624100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1840700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>646700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>513200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>338800</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>504700</v>
+        <v>59500</v>
       </c>
       <c r="E61" s="3">
-        <v>176100</v>
+        <v>508100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>177300</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2734,51 +2876,57 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>470000</v>
+        <v>496400</v>
       </c>
       <c r="E62" s="3">
-        <v>337400</v>
+        <v>473200</v>
       </c>
       <c r="F62" s="3">
-        <v>184600</v>
+        <v>339700</v>
       </c>
       <c r="G62" s="3">
-        <v>115800</v>
+        <v>185900</v>
       </c>
       <c r="H62" s="3">
-        <v>61000</v>
+        <v>116600</v>
       </c>
       <c r="I62" s="3">
-        <v>32000</v>
+        <v>61400</v>
       </c>
       <c r="J62" s="3">
+        <v>32200</v>
+      </c>
+      <c r="K62" s="3">
         <v>54200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>26300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>22100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9500</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>9393500</v>
+        <v>8569100</v>
       </c>
       <c r="E66" s="3">
-        <v>8052300</v>
+        <v>9457500</v>
       </c>
       <c r="F66" s="3">
-        <v>8250000</v>
+        <v>8107100</v>
       </c>
       <c r="G66" s="3">
-        <v>6996600</v>
+        <v>8306100</v>
       </c>
       <c r="H66" s="3">
-        <v>5762900</v>
+        <v>7044200</v>
       </c>
       <c r="I66" s="3">
-        <v>3493300</v>
+        <v>5802200</v>
       </c>
       <c r="J66" s="3">
+        <v>3517100</v>
+      </c>
+      <c r="K66" s="3">
         <v>2739600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1658900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1880100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>657100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>516100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>344000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>12752100</v>
+      <c r="D72" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E72" s="3">
-        <v>10872400</v>
+        <v>12839000</v>
       </c>
       <c r="F72" s="3">
-        <v>9029200</v>
+        <v>10946400</v>
       </c>
       <c r="G72" s="3">
-        <v>7954600</v>
+        <v>9090700</v>
       </c>
       <c r="H72" s="3">
-        <v>6242900</v>
+        <v>8008800</v>
       </c>
       <c r="I72" s="3">
-        <v>6067100</v>
+        <v>6285400</v>
       </c>
       <c r="J72" s="3">
+        <v>6108400</v>
+      </c>
+      <c r="K72" s="3">
         <v>5038400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3818300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4327500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2827800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2053100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1728800</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>14461300</v>
+        <v>17278200</v>
       </c>
       <c r="E76" s="3">
-        <v>13162900</v>
+        <v>14559700</v>
       </c>
       <c r="F76" s="3">
-        <v>11340100</v>
+        <v>13252500</v>
       </c>
       <c r="G76" s="3">
-        <v>8485500</v>
+        <v>11417300</v>
       </c>
       <c r="H76" s="3">
-        <v>6245600</v>
+        <v>8543300</v>
       </c>
       <c r="I76" s="3">
-        <v>6314700</v>
+        <v>6288100</v>
       </c>
       <c r="J76" s="3">
+        <v>6357700</v>
+      </c>
+      <c r="K76" s="3">
         <v>5273400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4070200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4612900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3093100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2249900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1948100</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2808200</v>
+        <v>4089500</v>
       </c>
       <c r="E81" s="3">
-        <v>2327600</v>
+        <v>2827300</v>
       </c>
       <c r="F81" s="3">
-        <v>1665600</v>
+        <v>2343400</v>
       </c>
       <c r="G81" s="3">
-        <v>2932500</v>
+        <v>1677000</v>
       </c>
       <c r="H81" s="3">
-        <v>849500</v>
+        <v>2952400</v>
       </c>
       <c r="I81" s="3">
-        <v>1478600</v>
+        <v>855300</v>
       </c>
       <c r="J81" s="3">
+        <v>1488600</v>
+      </c>
+      <c r="K81" s="3">
         <v>1602400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>937500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>750400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>678900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>521900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>480000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>394700</v>
+        <v>424700</v>
       </c>
       <c r="E83" s="3">
-        <v>452300</v>
+        <v>397300</v>
       </c>
       <c r="F83" s="3">
-        <v>477500</v>
+        <v>455400</v>
       </c>
       <c r="G83" s="3">
-        <v>360900</v>
+        <v>480700</v>
       </c>
       <c r="H83" s="3">
-        <v>287700</v>
+        <v>363400</v>
       </c>
       <c r="I83" s="3">
-        <v>110700</v>
+        <v>289600</v>
       </c>
       <c r="J83" s="3">
+        <v>111500</v>
+      </c>
+      <c r="K83" s="3">
         <v>45200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>25400</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O83" s="3">
         <v>33500</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3826100</v>
+        <v>4911800</v>
       </c>
       <c r="E89" s="3">
-        <v>3441900</v>
+        <v>3852100</v>
       </c>
       <c r="F89" s="3">
-        <v>3436600</v>
+        <v>3465300</v>
       </c>
       <c r="G89" s="3">
-        <v>2377200</v>
+        <v>3460000</v>
       </c>
       <c r="H89" s="3">
-        <v>1852500</v>
+        <v>2393400</v>
       </c>
       <c r="I89" s="3">
-        <v>1641700</v>
+        <v>1865100</v>
       </c>
       <c r="J89" s="3">
+        <v>1652800</v>
+      </c>
+      <c r="K89" s="3">
         <v>2138600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1124300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>926500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>799900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>606100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>604500</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-290000</v>
+        <v>-320000</v>
       </c>
       <c r="E91" s="3">
-        <v>-221200</v>
+        <v>-292000</v>
       </c>
       <c r="F91" s="3">
-        <v>-145800</v>
+        <v>-222700</v>
       </c>
       <c r="G91" s="3">
-        <v>-167000</v>
+        <v>-146700</v>
       </c>
       <c r="H91" s="3">
-        <v>-349100</v>
+        <v>-168100</v>
       </c>
       <c r="I91" s="3">
-        <v>-254500</v>
+        <v>-351500</v>
       </c>
       <c r="J91" s="3">
+        <v>-256200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-156800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-120600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-84800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-33400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-25600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-60900</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1017600</v>
+        <v>-2369400</v>
       </c>
       <c r="E94" s="3">
-        <v>-977400</v>
+        <v>-1024500</v>
       </c>
       <c r="F94" s="3">
-        <v>-4030900</v>
+        <v>-984000</v>
       </c>
       <c r="G94" s="3">
-        <v>-3056600</v>
+        <v>-4058300</v>
       </c>
       <c r="H94" s="3">
-        <v>-1873700</v>
+        <v>-3077400</v>
       </c>
       <c r="I94" s="3">
-        <v>-1775100</v>
+        <v>-1886400</v>
       </c>
       <c r="J94" s="3">
+        <v>-1787100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1637800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-353100</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O94" s="3">
         <v>-639100</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-928400</v>
+        <v>-1114100</v>
       </c>
       <c r="E96" s="3">
-        <v>-484400</v>
+        <v>-934700</v>
       </c>
       <c r="F96" s="3">
-        <v>-591000</v>
+        <v>-487700</v>
       </c>
       <c r="G96" s="3">
-        <v>-1220700</v>
+        <v>-595100</v>
       </c>
       <c r="H96" s="3">
-        <v>-198900</v>
+        <v>-1229000</v>
       </c>
       <c r="I96" s="3">
-        <v>-449800</v>
+        <v>-200200</v>
       </c>
       <c r="J96" s="3">
+        <v>-452900</v>
+      </c>
+      <c r="K96" s="3">
         <v>-351600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-204300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-312800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-124600</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1413600</v>
+        <v>-2984300</v>
       </c>
       <c r="E100" s="3">
-        <v>-1737800</v>
+        <v>-1423200</v>
       </c>
       <c r="F100" s="3">
-        <v>1368800</v>
+        <v>-1749600</v>
       </c>
       <c r="G100" s="3">
-        <v>149500</v>
+        <v>1378100</v>
       </c>
       <c r="H100" s="3">
-        <v>219200</v>
+        <v>150500</v>
       </c>
       <c r="I100" s="3">
-        <v>-179900</v>
+        <v>220700</v>
       </c>
       <c r="J100" s="3">
+        <v>-181100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-310800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-227300</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O100" s="3">
         <v>-56000</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>15200</v>
+        <v>-28100</v>
       </c>
       <c r="E101" s="3">
-        <v>-7600</v>
+        <v>15300</v>
       </c>
       <c r="F101" s="3">
-        <v>22400</v>
+        <v>-7700</v>
       </c>
       <c r="G101" s="3">
+        <v>22500</v>
+      </c>
+      <c r="H101" s="3">
         <v>4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>11300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>18300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>19800</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1410100</v>
+        <v>-470100</v>
       </c>
       <c r="E102" s="3">
-        <v>719100</v>
+        <v>1419700</v>
       </c>
       <c r="F102" s="3">
-        <v>796800</v>
+        <v>723900</v>
       </c>
       <c r="G102" s="3">
-        <v>-525900</v>
+        <v>802200</v>
       </c>
       <c r="H102" s="3">
-        <v>209200</v>
+        <v>-529500</v>
       </c>
       <c r="I102" s="3">
-        <v>-315000</v>
+        <v>210700</v>
       </c>
       <c r="J102" s="3">
+        <v>-317200</v>
+      </c>
+      <c r="K102" s="3">
         <v>208300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>563800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>88800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-20200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-89500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>137900</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NTES_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NTES_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>NTES</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14384100</v>
+        <v>14295200</v>
       </c>
       <c r="E8" s="3">
-        <v>13414800</v>
+        <v>13331900</v>
       </c>
       <c r="F8" s="3">
-        <v>12179000</v>
+        <v>12103600</v>
       </c>
       <c r="G8" s="3">
-        <v>10241200</v>
+        <v>10177900</v>
       </c>
       <c r="H8" s="3">
-        <v>8235700</v>
+        <v>8184800</v>
       </c>
       <c r="I8" s="3">
-        <v>7114800</v>
+        <v>7070800</v>
       </c>
       <c r="J8" s="3">
-        <v>6177700</v>
+        <v>6139500</v>
       </c>
       <c r="K8" s="3">
         <v>4693900</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>5617100</v>
+        <v>5582300</v>
       </c>
       <c r="E9" s="3">
-        <v>6079300</v>
+        <v>6041700</v>
       </c>
       <c r="F9" s="3">
-        <v>5649100</v>
+        <v>5614200</v>
       </c>
       <c r="G9" s="3">
-        <v>4821700</v>
+        <v>4791900</v>
       </c>
       <c r="H9" s="3">
-        <v>3848900</v>
+        <v>3825100</v>
       </c>
       <c r="I9" s="3">
-        <v>3313200</v>
+        <v>3292700</v>
       </c>
       <c r="J9" s="3">
-        <v>2696200</v>
+        <v>2679500</v>
       </c>
       <c r="K9" s="3">
         <v>4052500</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>8767100</v>
+        <v>8712800</v>
       </c>
       <c r="E10" s="3">
-        <v>7335500</v>
+        <v>7290200</v>
       </c>
       <c r="F10" s="3">
-        <v>6529900</v>
+        <v>6489500</v>
       </c>
       <c r="G10" s="3">
-        <v>5419500</v>
+        <v>5385900</v>
       </c>
       <c r="H10" s="3">
-        <v>4386800</v>
+        <v>4359700</v>
       </c>
       <c r="I10" s="3">
-        <v>3801700</v>
+        <v>3778100</v>
       </c>
       <c r="J10" s="3">
-        <v>3481500</v>
+        <v>3459900</v>
       </c>
       <c r="K10" s="3">
         <v>641400</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>2291700</v>
+        <v>2277600</v>
       </c>
       <c r="E12" s="3">
-        <v>2090700</v>
+        <v>2077800</v>
       </c>
       <c r="F12" s="3">
-        <v>1956800</v>
+        <v>1944700</v>
       </c>
       <c r="G12" s="3">
-        <v>1441600</v>
+        <v>1432600</v>
       </c>
       <c r="H12" s="3">
-        <v>1169600</v>
+        <v>1162400</v>
       </c>
       <c r="I12" s="3">
-        <v>1025800</v>
+        <v>1019400</v>
       </c>
       <c r="J12" s="3">
-        <v>578600</v>
+        <v>575000</v>
       </c>
       <c r="K12" s="3">
         <v>823900</v>
@@ -969,8 +969,8 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>17</v>
+      <c r="D14" s="3">
+        <v>-37900</v>
       </c>
       <c r="E14" s="3">
         <v>7700</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>10532000</v>
+        <v>10429000</v>
       </c>
       <c r="E17" s="3">
-        <v>10693800</v>
+        <v>10627700</v>
       </c>
       <c r="F17" s="3">
-        <v>9899400</v>
+        <v>9838100</v>
       </c>
       <c r="G17" s="3">
-        <v>8227800</v>
+        <v>8176900</v>
       </c>
       <c r="H17" s="3">
-        <v>6318500</v>
+        <v>6279400</v>
       </c>
       <c r="I17" s="3">
-        <v>5727800</v>
+        <v>5692400</v>
       </c>
       <c r="J17" s="3">
-        <v>4371100</v>
+        <v>4344100</v>
       </c>
       <c r="K17" s="3">
         <v>2902700</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>3852100</v>
+        <v>3866200</v>
       </c>
       <c r="E18" s="3">
-        <v>2721000</v>
+        <v>2704200</v>
       </c>
       <c r="F18" s="3">
-        <v>2279600</v>
+        <v>2265500</v>
       </c>
       <c r="G18" s="3">
-        <v>2013400</v>
+        <v>2000900</v>
       </c>
       <c r="H18" s="3">
-        <v>1917200</v>
+        <v>1905300</v>
       </c>
       <c r="I18" s="3">
-        <v>1387100</v>
+        <v>1378500</v>
       </c>
       <c r="J18" s="3">
-        <v>1806600</v>
+        <v>1795400</v>
       </c>
       <c r="K18" s="3">
         <v>1791300</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>882500</v>
+        <v>961300</v>
       </c>
       <c r="E20" s="3">
-        <v>740600</v>
+        <v>736000</v>
       </c>
       <c r="F20" s="3">
-        <v>680900</v>
+        <v>676700</v>
       </c>
       <c r="G20" s="3">
-        <v>158100</v>
+        <v>157100</v>
       </c>
       <c r="H20" s="3">
-        <v>418700</v>
+        <v>416100</v>
       </c>
       <c r="I20" s="3">
-        <v>196800</v>
+        <v>195500</v>
       </c>
       <c r="J20" s="3">
-        <v>130200</v>
+        <v>129400</v>
       </c>
       <c r="K20" s="3">
         <v>179100</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>5159800</v>
+        <v>5248600</v>
       </c>
       <c r="E21" s="3">
-        <v>3859400</v>
+        <v>3834300</v>
       </c>
       <c r="F21" s="3">
-        <v>3416400</v>
+        <v>3393800</v>
       </c>
       <c r="G21" s="3">
-        <v>2652700</v>
+        <v>2634700</v>
       </c>
       <c r="H21" s="3">
-        <v>2699600</v>
+        <v>2681700</v>
       </c>
       <c r="I21" s="3">
-        <v>1873700</v>
+        <v>1861200</v>
       </c>
       <c r="J21" s="3">
-        <v>2048400</v>
+        <v>2035300</v>
       </c>
       <c r="K21" s="3">
         <v>2015600</v>
@@ -1274,26 +1274,26 @@
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>17</v>
+      <c r="D22" s="3">
+        <v>122100</v>
       </c>
       <c r="E22" s="3">
-        <v>90400</v>
+        <v>89800</v>
       </c>
       <c r="F22" s="3">
-        <v>26600</v>
+        <v>26400</v>
       </c>
       <c r="G22" s="3">
-        <v>34400</v>
+        <v>34200</v>
       </c>
       <c r="H22" s="3">
-        <v>58300</v>
+        <v>57900</v>
       </c>
       <c r="I22" s="3">
-        <v>43900</v>
+        <v>43600</v>
       </c>
       <c r="J22" s="3">
-        <v>12800</v>
+        <v>12700</v>
       </c>
       <c r="K22" s="3">
         <v>4400</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4734600</v>
+        <v>4705300</v>
       </c>
       <c r="E23" s="3">
-        <v>3371300</v>
+        <v>3350400</v>
       </c>
       <c r="F23" s="3">
-        <v>2933900</v>
+        <v>2915800</v>
       </c>
       <c r="G23" s="3">
-        <v>2137000</v>
+        <v>2123800</v>
       </c>
       <c r="H23" s="3">
-        <v>2277600</v>
+        <v>2263500</v>
       </c>
       <c r="I23" s="3">
-        <v>1539900</v>
+        <v>1530400</v>
       </c>
       <c r="J23" s="3">
-        <v>1924000</v>
+        <v>1912100</v>
       </c>
       <c r="K23" s="3">
         <v>1965900</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>653400</v>
+        <v>649300</v>
       </c>
       <c r="E24" s="3">
-        <v>699500</v>
+        <v>695200</v>
       </c>
       <c r="F24" s="3">
-        <v>573900</v>
+        <v>570400</v>
       </c>
       <c r="G24" s="3">
-        <v>422900</v>
+        <v>420300</v>
       </c>
       <c r="H24" s="3">
-        <v>405200</v>
+        <v>402700</v>
       </c>
       <c r="I24" s="3">
-        <v>342100</v>
+        <v>340000</v>
       </c>
       <c r="J24" s="3">
-        <v>299700</v>
+        <v>297900</v>
       </c>
       <c r="K24" s="3">
         <v>290300</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4081200</v>
+        <v>4056000</v>
       </c>
       <c r="E26" s="3">
-        <v>2671700</v>
+        <v>2655200</v>
       </c>
       <c r="F26" s="3">
-        <v>2360000</v>
+        <v>2345400</v>
       </c>
       <c r="G26" s="3">
-        <v>1714100</v>
+        <v>1703500</v>
       </c>
       <c r="H26" s="3">
-        <v>1872400</v>
+        <v>1860800</v>
       </c>
       <c r="I26" s="3">
-        <v>1197800</v>
+        <v>1190400</v>
       </c>
       <c r="J26" s="3">
-        <v>1624300</v>
+        <v>1614200</v>
       </c>
       <c r="K26" s="3">
         <v>1675700</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4089500</v>
+        <v>4064200</v>
       </c>
       <c r="E27" s="3">
-        <v>2740500</v>
+        <v>2723500</v>
       </c>
       <c r="F27" s="3">
-        <v>2343400</v>
+        <v>2328900</v>
       </c>
       <c r="G27" s="3">
-        <v>1677000</v>
+        <v>1666600</v>
       </c>
       <c r="H27" s="3">
-        <v>1845500</v>
+        <v>1834100</v>
       </c>
       <c r="I27" s="3">
-        <v>1152600</v>
+        <v>1145500</v>
       </c>
       <c r="J27" s="3">
-        <v>1604600</v>
+        <v>1594700</v>
       </c>
       <c r="K27" s="3">
         <v>1649600</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>86900</v>
+        <v>86300</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -1602,13 +1602,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>1106900</v>
+        <v>1100100</v>
       </c>
       <c r="I29" s="3">
-        <v>-297300</v>
+        <v>-295500</v>
       </c>
       <c r="J29" s="3">
-        <v>-116000</v>
+        <v>-115300</v>
       </c>
       <c r="K29" s="3">
         <v>-47300</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-882500</v>
+        <v>-961300</v>
       </c>
       <c r="E32" s="3">
-        <v>-740600</v>
+        <v>-736000</v>
       </c>
       <c r="F32" s="3">
-        <v>-680900</v>
+        <v>-676700</v>
       </c>
       <c r="G32" s="3">
-        <v>-158100</v>
+        <v>-157100</v>
       </c>
       <c r="H32" s="3">
-        <v>-418700</v>
+        <v>-416100</v>
       </c>
       <c r="I32" s="3">
-        <v>-196800</v>
+        <v>-195500</v>
       </c>
       <c r="J32" s="3">
-        <v>-130200</v>
+        <v>-129400</v>
       </c>
       <c r="K32" s="3">
         <v>-179100</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4089500</v>
+        <v>4064200</v>
       </c>
       <c r="E33" s="3">
-        <v>2827300</v>
+        <v>2809800</v>
       </c>
       <c r="F33" s="3">
-        <v>2343400</v>
+        <v>2328900</v>
       </c>
       <c r="G33" s="3">
-        <v>1677000</v>
+        <v>1666600</v>
       </c>
       <c r="H33" s="3">
-        <v>2952400</v>
+        <v>2934200</v>
       </c>
       <c r="I33" s="3">
-        <v>855300</v>
+        <v>850000</v>
       </c>
       <c r="J33" s="3">
-        <v>1488600</v>
+        <v>1479400</v>
       </c>
       <c r="K33" s="3">
         <v>1602400</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4089500</v>
+        <v>4064200</v>
       </c>
       <c r="E35" s="3">
-        <v>2827300</v>
+        <v>2809800</v>
       </c>
       <c r="F35" s="3">
-        <v>2343400</v>
+        <v>2328900</v>
       </c>
       <c r="G35" s="3">
-        <v>1677000</v>
+        <v>1666600</v>
       </c>
       <c r="H35" s="3">
-        <v>2952400</v>
+        <v>2934200</v>
       </c>
       <c r="I35" s="3">
-        <v>855300</v>
+        <v>850000</v>
       </c>
       <c r="J35" s="3">
-        <v>1488600</v>
+        <v>1479400</v>
       </c>
       <c r="K35" s="3">
         <v>1602400</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2979000</v>
+        <v>2960600</v>
       </c>
       <c r="E41" s="3">
-        <v>3460100</v>
+        <v>3438700</v>
       </c>
       <c r="F41" s="3">
-        <v>2015500</v>
+        <v>2003100</v>
       </c>
       <c r="G41" s="3">
-        <v>1267500</v>
+        <v>1259600</v>
       </c>
       <c r="H41" s="3">
-        <v>451300</v>
+        <v>448500</v>
       </c>
       <c r="I41" s="3">
-        <v>693500</v>
+        <v>689200</v>
       </c>
       <c r="J41" s="3">
-        <v>384300</v>
+        <v>381900</v>
       </c>
       <c r="K41" s="3">
         <v>751100</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>14637700</v>
+        <v>14547200</v>
       </c>
       <c r="E42" s="3">
-        <v>12869100</v>
+        <v>12789500</v>
       </c>
       <c r="F42" s="3">
-        <v>11543700</v>
+        <v>11472300</v>
       </c>
       <c r="G42" s="3">
-        <v>11726700</v>
+        <v>11654100</v>
       </c>
       <c r="H42" s="3">
-        <v>9564500</v>
+        <v>9505400</v>
       </c>
       <c r="I42" s="3">
-        <v>6196800</v>
+        <v>6158500</v>
       </c>
       <c r="J42" s="3">
-        <v>5608900</v>
+        <v>5574200</v>
       </c>
       <c r="K42" s="3">
         <v>4272600</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>892800</v>
+        <v>1283800</v>
       </c>
       <c r="E43" s="3">
-        <v>906400</v>
+        <v>900800</v>
       </c>
       <c r="F43" s="3">
-        <v>991400</v>
+        <v>985300</v>
       </c>
       <c r="G43" s="3">
-        <v>931400</v>
+        <v>925700</v>
       </c>
       <c r="H43" s="3">
-        <v>666500</v>
+        <v>662400</v>
       </c>
       <c r="I43" s="3">
-        <v>1248800</v>
+        <v>1241100</v>
       </c>
       <c r="J43" s="3">
-        <v>573200</v>
+        <v>569700</v>
       </c>
       <c r="K43" s="3">
         <v>1225200</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>96700</v>
+        <v>96100</v>
       </c>
       <c r="E44" s="3">
-        <v>138100</v>
+        <v>137300</v>
       </c>
       <c r="F44" s="3">
-        <v>134100</v>
+        <v>133300</v>
       </c>
       <c r="G44" s="3">
-        <v>86400</v>
+        <v>85800</v>
       </c>
       <c r="H44" s="3">
-        <v>90400</v>
+        <v>89900</v>
       </c>
       <c r="I44" s="3">
-        <v>148100</v>
+        <v>147200</v>
       </c>
       <c r="J44" s="3">
-        <v>761100</v>
+        <v>756400</v>
       </c>
       <c r="K44" s="3">
         <v>217900</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1230900</v>
+        <v>826800</v>
       </c>
       <c r="E45" s="3">
-        <v>921700</v>
+        <v>916000</v>
       </c>
       <c r="F45" s="3">
-        <v>1041200</v>
+        <v>1034700</v>
       </c>
       <c r="G45" s="3">
-        <v>978800</v>
+        <v>972700</v>
       </c>
       <c r="H45" s="3">
-        <v>1058500</v>
+        <v>1051900</v>
       </c>
       <c r="I45" s="3">
-        <v>2505200</v>
+        <v>2489700</v>
       </c>
       <c r="J45" s="3">
-        <v>1284500</v>
+        <v>1276500</v>
       </c>
       <c r="K45" s="3">
         <v>1741600</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>19837100</v>
+        <v>19714400</v>
       </c>
       <c r="E46" s="3">
-        <v>18295500</v>
+        <v>18182300</v>
       </c>
       <c r="F46" s="3">
-        <v>15726000</v>
+        <v>15628700</v>
       </c>
       <c r="G46" s="3">
-        <v>14990700</v>
+        <v>14897900</v>
       </c>
       <c r="H46" s="3">
-        <v>11831300</v>
+        <v>11758100</v>
       </c>
       <c r="I46" s="3">
-        <v>9552900</v>
+        <v>9493800</v>
       </c>
       <c r="J46" s="3">
-        <v>8612000</v>
+        <v>8558700</v>
       </c>
       <c r="K46" s="3">
         <v>6818900</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>146000</v>
+        <v>3367200</v>
       </c>
       <c r="E47" s="3">
-        <v>3233200</v>
+        <v>3213200</v>
       </c>
       <c r="F47" s="3">
-        <v>3445700</v>
+        <v>3424400</v>
       </c>
       <c r="G47" s="3">
-        <v>2577300</v>
+        <v>2561400</v>
       </c>
       <c r="H47" s="3">
-        <v>1842500</v>
+        <v>1831100</v>
       </c>
       <c r="I47" s="3">
-        <v>743200</v>
+        <v>738600</v>
       </c>
       <c r="J47" s="3">
-        <v>387100</v>
+        <v>384700</v>
       </c>
       <c r="K47" s="3">
         <v>348000</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1122600</v>
+        <v>1219200</v>
       </c>
       <c r="E48" s="3">
-        <v>1005200</v>
+        <v>998900</v>
       </c>
       <c r="F48" s="3">
-        <v>900600</v>
+        <v>895000</v>
       </c>
       <c r="G48" s="3">
-        <v>740800</v>
+        <v>736200</v>
       </c>
       <c r="H48" s="3">
-        <v>707000</v>
+        <v>702600</v>
       </c>
       <c r="I48" s="3">
-        <v>1397400</v>
+        <v>1388700</v>
       </c>
       <c r="J48" s="3">
-        <v>524000</v>
+        <v>520800</v>
       </c>
       <c r="K48" s="3">
         <v>668200</v>
@@ -2352,26 +2352,26 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>17</v>
+      <c r="D49" s="3">
+        <v>516700</v>
       </c>
       <c r="E49" s="3">
-        <v>595600</v>
+        <v>591900</v>
       </c>
       <c r="F49" s="3">
-        <v>446600</v>
+        <v>443800</v>
       </c>
       <c r="G49" s="3">
-        <v>617900</v>
+        <v>614000</v>
       </c>
       <c r="H49" s="3">
-        <v>505900</v>
+        <v>502800</v>
       </c>
       <c r="I49" s="3">
-        <v>342700</v>
+        <v>340600</v>
       </c>
       <c r="J49" s="3">
-        <v>114000</v>
+        <v>113300</v>
       </c>
       <c r="K49" s="3">
         <v>35100</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4741600</v>
+        <v>869900</v>
       </c>
       <c r="E52" s="3">
-        <v>887800</v>
+        <v>882300</v>
       </c>
       <c r="F52" s="3">
-        <v>840700</v>
+        <v>835500</v>
       </c>
       <c r="G52" s="3">
-        <v>796800</v>
+        <v>791900</v>
       </c>
       <c r="H52" s="3">
-        <v>700800</v>
+        <v>696500</v>
       </c>
       <c r="I52" s="3">
-        <v>1942800</v>
+        <v>1930800</v>
       </c>
       <c r="J52" s="3">
-        <v>237600</v>
+        <v>236100</v>
       </c>
       <c r="K52" s="3">
         <v>818100</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>25847300</v>
+        <v>25687400</v>
       </c>
       <c r="E54" s="3">
-        <v>24017200</v>
+        <v>23868700</v>
       </c>
       <c r="F54" s="3">
-        <v>21359600</v>
+        <v>21227400</v>
       </c>
       <c r="G54" s="3">
-        <v>19723400</v>
+        <v>19601400</v>
       </c>
       <c r="H54" s="3">
-        <v>15587500</v>
+        <v>15491100</v>
       </c>
       <c r="I54" s="3">
-        <v>12090300</v>
+        <v>12015500</v>
       </c>
       <c r="J54" s="3">
-        <v>9874800</v>
+        <v>9813700</v>
       </c>
       <c r="K54" s="3">
         <v>8013000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>122500</v>
+        <v>121700</v>
       </c>
       <c r="E57" s="3">
-        <v>209500</v>
+        <v>208200</v>
       </c>
       <c r="F57" s="3">
-        <v>136900</v>
+        <v>136100</v>
       </c>
       <c r="G57" s="3">
-        <v>157700</v>
+        <v>156700</v>
       </c>
       <c r="H57" s="3">
-        <v>168500</v>
+        <v>167500</v>
       </c>
       <c r="I57" s="3">
-        <v>167100</v>
+        <v>166000</v>
       </c>
       <c r="J57" s="3">
-        <v>339600</v>
+        <v>337500</v>
       </c>
       <c r="K57" s="3">
         <v>192800</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2674800</v>
+        <v>2658200</v>
       </c>
       <c r="E58" s="3">
-        <v>3319200</v>
+        <v>3298700</v>
       </c>
       <c r="F58" s="3">
-        <v>2690400</v>
+        <v>2673700</v>
       </c>
       <c r="G58" s="3">
-        <v>2711500</v>
+        <v>2694800</v>
       </c>
       <c r="H58" s="3">
-        <v>2339500</v>
+        <v>2325000</v>
       </c>
       <c r="I58" s="3">
-        <v>1898800</v>
+        <v>1887100</v>
       </c>
       <c r="J58" s="3">
-        <v>920800</v>
+        <v>915100</v>
       </c>
       <c r="K58" s="3">
         <v>526900</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4687900</v>
+        <v>4658900</v>
       </c>
       <c r="E59" s="3">
-        <v>4371600</v>
+        <v>4344600</v>
       </c>
       <c r="F59" s="3">
-        <v>4193400</v>
+        <v>4167500</v>
       </c>
       <c r="G59" s="3">
-        <v>3629000</v>
+        <v>3606600</v>
       </c>
       <c r="H59" s="3">
-        <v>2808500</v>
+        <v>2791200</v>
       </c>
       <c r="I59" s="3">
-        <v>3628000</v>
+        <v>3605600</v>
       </c>
       <c r="J59" s="3">
-        <v>2041400</v>
+        <v>2028800</v>
       </c>
       <c r="K59" s="3">
         <v>2422300</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7485200</v>
+        <v>7438900</v>
       </c>
       <c r="E60" s="3">
-        <v>7900300</v>
+        <v>7851500</v>
       </c>
       <c r="F60" s="3">
-        <v>7020700</v>
+        <v>6977300</v>
       </c>
       <c r="G60" s="3">
-        <v>6498300</v>
+        <v>6458100</v>
       </c>
       <c r="H60" s="3">
-        <v>5316500</v>
+        <v>5283700</v>
       </c>
       <c r="I60" s="3">
-        <v>4880900</v>
+        <v>4850700</v>
       </c>
       <c r="J60" s="3">
-        <v>3301700</v>
+        <v>3281300</v>
       </c>
       <c r="K60" s="3">
         <v>2647900</v>
@@ -2841,13 +2841,13 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>59500</v>
+        <v>59100</v>
       </c>
       <c r="E61" s="3">
-        <v>508100</v>
+        <v>505000</v>
       </c>
       <c r="F61" s="3">
-        <v>177300</v>
+        <v>176200</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>496400</v>
+        <v>493300</v>
       </c>
       <c r="E62" s="3">
-        <v>473200</v>
+        <v>470300</v>
       </c>
       <c r="F62" s="3">
-        <v>339700</v>
+        <v>337600</v>
       </c>
       <c r="G62" s="3">
-        <v>185900</v>
+        <v>184700</v>
       </c>
       <c r="H62" s="3">
-        <v>116600</v>
+        <v>115900</v>
       </c>
       <c r="I62" s="3">
-        <v>61400</v>
+        <v>61000</v>
       </c>
       <c r="J62" s="3">
-        <v>32200</v>
+        <v>32000</v>
       </c>
       <c r="K62" s="3">
         <v>54200</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>8569100</v>
+        <v>8516100</v>
       </c>
       <c r="E66" s="3">
-        <v>9457500</v>
+        <v>9399000</v>
       </c>
       <c r="F66" s="3">
-        <v>8107100</v>
+        <v>8056900</v>
       </c>
       <c r="G66" s="3">
-        <v>8306100</v>
+        <v>8254800</v>
       </c>
       <c r="H66" s="3">
-        <v>7044200</v>
+        <v>7000700</v>
       </c>
       <c r="I66" s="3">
-        <v>5802200</v>
+        <v>5766300</v>
       </c>
       <c r="J66" s="3">
-        <v>3517100</v>
+        <v>3495400</v>
       </c>
       <c r="K66" s="3">
         <v>2739600</v>
@@ -3309,26 +3309,26 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>17</v>
+      <c r="D72" s="3">
+        <v>15716500</v>
       </c>
       <c r="E72" s="3">
-        <v>12839000</v>
+        <v>12759500</v>
       </c>
       <c r="F72" s="3">
-        <v>10946400</v>
+        <v>10878700</v>
       </c>
       <c r="G72" s="3">
-        <v>9090700</v>
+        <v>9034400</v>
       </c>
       <c r="H72" s="3">
-        <v>8008800</v>
+        <v>7959200</v>
       </c>
       <c r="I72" s="3">
-        <v>6285400</v>
+        <v>6246500</v>
       </c>
       <c r="J72" s="3">
-        <v>6108400</v>
+        <v>6070700</v>
       </c>
       <c r="K72" s="3">
         <v>5038400</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>17278200</v>
+        <v>17171300</v>
       </c>
       <c r="E76" s="3">
-        <v>14559700</v>
+        <v>14469700</v>
       </c>
       <c r="F76" s="3">
-        <v>13252500</v>
+        <v>13170500</v>
       </c>
       <c r="G76" s="3">
-        <v>11417300</v>
+        <v>11346600</v>
       </c>
       <c r="H76" s="3">
-        <v>8543300</v>
+        <v>8490400</v>
       </c>
       <c r="I76" s="3">
-        <v>6288100</v>
+        <v>6249200</v>
       </c>
       <c r="J76" s="3">
-        <v>6357700</v>
+        <v>6318300</v>
       </c>
       <c r="K76" s="3">
         <v>5273400</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4089500</v>
+        <v>4064200</v>
       </c>
       <c r="E81" s="3">
-        <v>2827300</v>
+        <v>2809800</v>
       </c>
       <c r="F81" s="3">
-        <v>2343400</v>
+        <v>2328900</v>
       </c>
       <c r="G81" s="3">
-        <v>1677000</v>
+        <v>1666600</v>
       </c>
       <c r="H81" s="3">
-        <v>2952400</v>
+        <v>2934200</v>
       </c>
       <c r="I81" s="3">
-        <v>855300</v>
+        <v>850000</v>
       </c>
       <c r="J81" s="3">
-        <v>1488600</v>
+        <v>1479400</v>
       </c>
       <c r="K81" s="3">
         <v>1602400</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>424700</v>
+        <v>422100</v>
       </c>
       <c r="E83" s="3">
-        <v>397300</v>
+        <v>394900</v>
       </c>
       <c r="F83" s="3">
-        <v>455400</v>
+        <v>452600</v>
       </c>
       <c r="G83" s="3">
-        <v>480700</v>
+        <v>477700</v>
       </c>
       <c r="H83" s="3">
-        <v>363400</v>
+        <v>361100</v>
       </c>
       <c r="I83" s="3">
-        <v>289600</v>
+        <v>287900</v>
       </c>
       <c r="J83" s="3">
-        <v>111500</v>
+        <v>110800</v>
       </c>
       <c r="K83" s="3">
         <v>45200</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4911800</v>
+        <v>4881400</v>
       </c>
       <c r="E89" s="3">
-        <v>3852100</v>
+        <v>3828300</v>
       </c>
       <c r="F89" s="3">
-        <v>3465300</v>
+        <v>3443900</v>
       </c>
       <c r="G89" s="3">
-        <v>3460000</v>
+        <v>3438500</v>
       </c>
       <c r="H89" s="3">
-        <v>2393400</v>
+        <v>2378600</v>
       </c>
       <c r="I89" s="3">
-        <v>1865100</v>
+        <v>1853500</v>
       </c>
       <c r="J89" s="3">
-        <v>1652800</v>
+        <v>1642600</v>
       </c>
       <c r="K89" s="3">
         <v>2138600</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-320000</v>
+        <v>-318000</v>
       </c>
       <c r="E91" s="3">
-        <v>-292000</v>
+        <v>-290200</v>
       </c>
       <c r="F91" s="3">
-        <v>-222700</v>
+        <v>-221300</v>
       </c>
       <c r="G91" s="3">
-        <v>-146700</v>
+        <v>-145800</v>
       </c>
       <c r="H91" s="3">
-        <v>-168100</v>
+        <v>-167100</v>
       </c>
       <c r="I91" s="3">
-        <v>-351500</v>
+        <v>-349300</v>
       </c>
       <c r="J91" s="3">
-        <v>-256200</v>
+        <v>-254600</v>
       </c>
       <c r="K91" s="3">
         <v>-156800</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2369400</v>
+        <v>-2354700</v>
       </c>
       <c r="E94" s="3">
-        <v>-1024500</v>
+        <v>-1018200</v>
       </c>
       <c r="F94" s="3">
-        <v>-984000</v>
+        <v>-977900</v>
       </c>
       <c r="G94" s="3">
-        <v>-4058300</v>
+        <v>-4033200</v>
       </c>
       <c r="H94" s="3">
-        <v>-3077400</v>
+        <v>-3058400</v>
       </c>
       <c r="I94" s="3">
-        <v>-1886400</v>
+        <v>-1874800</v>
       </c>
       <c r="J94" s="3">
-        <v>-1787100</v>
+        <v>-1776100</v>
       </c>
       <c r="K94" s="3">
         <v>-1637800</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1114100</v>
+        <v>-1107200</v>
       </c>
       <c r="E96" s="3">
-        <v>-934700</v>
+        <v>-928900</v>
       </c>
       <c r="F96" s="3">
-        <v>-487700</v>
+        <v>-484700</v>
       </c>
       <c r="G96" s="3">
-        <v>-595100</v>
+        <v>-591400</v>
       </c>
       <c r="H96" s="3">
-        <v>-1229000</v>
+        <v>-1221400</v>
       </c>
       <c r="I96" s="3">
-        <v>-200200</v>
+        <v>-199000</v>
       </c>
       <c r="J96" s="3">
-        <v>-452900</v>
+        <v>-450100</v>
       </c>
       <c r="K96" s="3">
         <v>-351600</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2984300</v>
+        <v>-2965900</v>
       </c>
       <c r="E100" s="3">
-        <v>-1423200</v>
+        <v>-1414400</v>
       </c>
       <c r="F100" s="3">
-        <v>-1749600</v>
+        <v>-1738800</v>
       </c>
       <c r="G100" s="3">
-        <v>1378100</v>
+        <v>1369600</v>
       </c>
       <c r="H100" s="3">
-        <v>150500</v>
+        <v>149600</v>
       </c>
       <c r="I100" s="3">
-        <v>220700</v>
+        <v>219300</v>
       </c>
       <c r="J100" s="3">
-        <v>-181100</v>
+        <v>-180000</v>
       </c>
       <c r="K100" s="3">
         <v>-310800</v>
@@ -4452,16 +4452,16 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-28100</v>
+        <v>-28000</v>
       </c>
       <c r="E101" s="3">
         <v>15300</v>
       </c>
       <c r="F101" s="3">
-        <v>-7700</v>
+        <v>-7600</v>
       </c>
       <c r="G101" s="3">
-        <v>22500</v>
+        <v>22400</v>
       </c>
       <c r="H101" s="3">
         <v>4000</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-470100</v>
+        <v>-467200</v>
       </c>
       <c r="E102" s="3">
-        <v>1419700</v>
+        <v>1410900</v>
       </c>
       <c r="F102" s="3">
-        <v>723900</v>
+        <v>719500</v>
       </c>
       <c r="G102" s="3">
-        <v>802200</v>
+        <v>797300</v>
       </c>
       <c r="H102" s="3">
-        <v>-529500</v>
+        <v>-526200</v>
       </c>
       <c r="I102" s="3">
-        <v>210700</v>
+        <v>209400</v>
       </c>
       <c r="J102" s="3">
-        <v>-317200</v>
+        <v>-315200</v>
       </c>
       <c r="K102" s="3">
         <v>208300</v>

--- a/AAII_Financials/Yearly/NTES_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NTES_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14295200</v>
+        <v>14586900</v>
       </c>
       <c r="E8" s="3">
-        <v>13331900</v>
+        <v>13604000</v>
       </c>
       <c r="F8" s="3">
-        <v>12103600</v>
+        <v>12350700</v>
       </c>
       <c r="G8" s="3">
-        <v>10177900</v>
+        <v>10385600</v>
       </c>
       <c r="H8" s="3">
-        <v>8184800</v>
+        <v>8351800</v>
       </c>
       <c r="I8" s="3">
-        <v>7070800</v>
+        <v>7215200</v>
       </c>
       <c r="J8" s="3">
-        <v>6139500</v>
+        <v>6264800</v>
       </c>
       <c r="K8" s="3">
         <v>4693900</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>5582300</v>
+        <v>5696300</v>
       </c>
       <c r="E9" s="3">
-        <v>6041700</v>
+        <v>6165000</v>
       </c>
       <c r="F9" s="3">
-        <v>5614200</v>
+        <v>5728800</v>
       </c>
       <c r="G9" s="3">
-        <v>4791900</v>
+        <v>4889700</v>
       </c>
       <c r="H9" s="3">
-        <v>3825100</v>
+        <v>3903200</v>
       </c>
       <c r="I9" s="3">
-        <v>3292700</v>
+        <v>3359900</v>
       </c>
       <c r="J9" s="3">
-        <v>2679500</v>
+        <v>2734200</v>
       </c>
       <c r="K9" s="3">
         <v>4052500</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>8712800</v>
+        <v>8890700</v>
       </c>
       <c r="E10" s="3">
-        <v>7290200</v>
+        <v>7439000</v>
       </c>
       <c r="F10" s="3">
-        <v>6489500</v>
+        <v>6621900</v>
       </c>
       <c r="G10" s="3">
-        <v>5385900</v>
+        <v>5495900</v>
       </c>
       <c r="H10" s="3">
-        <v>4359700</v>
+        <v>4448700</v>
       </c>
       <c r="I10" s="3">
-        <v>3778100</v>
+        <v>3855300</v>
       </c>
       <c r="J10" s="3">
-        <v>3459900</v>
+        <v>3530600</v>
       </c>
       <c r="K10" s="3">
         <v>641400</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>2277600</v>
+        <v>2324000</v>
       </c>
       <c r="E12" s="3">
-        <v>2077800</v>
+        <v>2120200</v>
       </c>
       <c r="F12" s="3">
-        <v>1944700</v>
+        <v>1984400</v>
       </c>
       <c r="G12" s="3">
-        <v>1432600</v>
+        <v>1461900</v>
       </c>
       <c r="H12" s="3">
-        <v>1162400</v>
+        <v>1186100</v>
       </c>
       <c r="I12" s="3">
-        <v>1019400</v>
+        <v>1040200</v>
       </c>
       <c r="J12" s="3">
-        <v>575000</v>
+        <v>586700</v>
       </c>
       <c r="K12" s="3">
         <v>823900</v>
@@ -970,16 +970,16 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-37900</v>
+        <v>-38700</v>
       </c>
       <c r="E14" s="3">
-        <v>7700</v>
+        <v>7800</v>
       </c>
       <c r="F14" s="3">
         <v>2700</v>
       </c>
       <c r="G14" s="3">
-        <v>7700</v>
+        <v>7800</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>17</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>10429000</v>
+        <v>10641800</v>
       </c>
       <c r="E17" s="3">
-        <v>10627700</v>
+        <v>10844600</v>
       </c>
       <c r="F17" s="3">
-        <v>9838100</v>
+        <v>10038900</v>
       </c>
       <c r="G17" s="3">
-        <v>8176900</v>
+        <v>8343800</v>
       </c>
       <c r="H17" s="3">
-        <v>6279400</v>
+        <v>6407600</v>
       </c>
       <c r="I17" s="3">
-        <v>5692400</v>
+        <v>5808500</v>
       </c>
       <c r="J17" s="3">
-        <v>4344100</v>
+        <v>4432800</v>
       </c>
       <c r="K17" s="3">
         <v>2902700</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>3866200</v>
+        <v>3945100</v>
       </c>
       <c r="E18" s="3">
-        <v>2704200</v>
+        <v>2759400</v>
       </c>
       <c r="F18" s="3">
-        <v>2265500</v>
+        <v>2311800</v>
       </c>
       <c r="G18" s="3">
-        <v>2000900</v>
+        <v>2041800</v>
       </c>
       <c r="H18" s="3">
-        <v>1905300</v>
+        <v>1944200</v>
       </c>
       <c r="I18" s="3">
-        <v>1378500</v>
+        <v>1406600</v>
       </c>
       <c r="J18" s="3">
-        <v>1795400</v>
+        <v>1832000</v>
       </c>
       <c r="K18" s="3">
         <v>1791300</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>961300</v>
+        <v>980900</v>
       </c>
       <c r="E20" s="3">
-        <v>736000</v>
+        <v>751100</v>
       </c>
       <c r="F20" s="3">
-        <v>676700</v>
+        <v>690500</v>
       </c>
       <c r="G20" s="3">
-        <v>157100</v>
+        <v>160300</v>
       </c>
       <c r="H20" s="3">
-        <v>416100</v>
+        <v>424600</v>
       </c>
       <c r="I20" s="3">
-        <v>195500</v>
+        <v>199500</v>
       </c>
       <c r="J20" s="3">
-        <v>129400</v>
+        <v>132100</v>
       </c>
       <c r="K20" s="3">
         <v>179100</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>5248600</v>
+        <v>5355300</v>
       </c>
       <c r="E21" s="3">
-        <v>3834300</v>
+        <v>3912000</v>
       </c>
       <c r="F21" s="3">
-        <v>3393800</v>
+        <v>3462500</v>
       </c>
       <c r="G21" s="3">
-        <v>2634700</v>
+        <v>2687900</v>
       </c>
       <c r="H21" s="3">
-        <v>2681700</v>
+        <v>2736000</v>
       </c>
       <c r="I21" s="3">
-        <v>1861200</v>
+        <v>1898900</v>
       </c>
       <c r="J21" s="3">
-        <v>2035300</v>
+        <v>2076700</v>
       </c>
       <c r="K21" s="3">
         <v>2015600</v>
@@ -1275,25 +1275,25 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>122100</v>
+        <v>124600</v>
       </c>
       <c r="E22" s="3">
-        <v>89800</v>
+        <v>91700</v>
       </c>
       <c r="F22" s="3">
-        <v>26400</v>
+        <v>27000</v>
       </c>
       <c r="G22" s="3">
-        <v>34200</v>
+        <v>34900</v>
       </c>
       <c r="H22" s="3">
-        <v>57900</v>
+        <v>59100</v>
       </c>
       <c r="I22" s="3">
-        <v>43600</v>
+        <v>44500</v>
       </c>
       <c r="J22" s="3">
-        <v>12700</v>
+        <v>13000</v>
       </c>
       <c r="K22" s="3">
         <v>4400</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4705300</v>
+        <v>4801300</v>
       </c>
       <c r="E23" s="3">
-        <v>3350400</v>
+        <v>3418800</v>
       </c>
       <c r="F23" s="3">
-        <v>2915800</v>
+        <v>2975300</v>
       </c>
       <c r="G23" s="3">
-        <v>2123800</v>
+        <v>2167200</v>
       </c>
       <c r="H23" s="3">
-        <v>2263500</v>
+        <v>2309700</v>
       </c>
       <c r="I23" s="3">
-        <v>1530400</v>
+        <v>1561600</v>
       </c>
       <c r="J23" s="3">
-        <v>1912100</v>
+        <v>1951100</v>
       </c>
       <c r="K23" s="3">
         <v>1965900</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>649300</v>
+        <v>662600</v>
       </c>
       <c r="E24" s="3">
-        <v>695200</v>
+        <v>709400</v>
       </c>
       <c r="F24" s="3">
-        <v>570400</v>
+        <v>582000</v>
       </c>
       <c r="G24" s="3">
-        <v>420300</v>
+        <v>428800</v>
       </c>
       <c r="H24" s="3">
-        <v>402700</v>
+        <v>410900</v>
       </c>
       <c r="I24" s="3">
-        <v>340000</v>
+        <v>346900</v>
       </c>
       <c r="J24" s="3">
-        <v>297900</v>
+        <v>304000</v>
       </c>
       <c r="K24" s="3">
         <v>290300</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4056000</v>
+        <v>4138800</v>
       </c>
       <c r="E26" s="3">
-        <v>2655200</v>
+        <v>2709400</v>
       </c>
       <c r="F26" s="3">
-        <v>2345400</v>
+        <v>2393300</v>
       </c>
       <c r="G26" s="3">
-        <v>1703500</v>
+        <v>1738300</v>
       </c>
       <c r="H26" s="3">
-        <v>1860800</v>
+        <v>1898800</v>
       </c>
       <c r="I26" s="3">
-        <v>1190400</v>
+        <v>1214700</v>
       </c>
       <c r="J26" s="3">
-        <v>1614200</v>
+        <v>1647200</v>
       </c>
       <c r="K26" s="3">
         <v>1675700</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4064200</v>
+        <v>4147100</v>
       </c>
       <c r="E27" s="3">
-        <v>2723500</v>
+        <v>2779100</v>
       </c>
       <c r="F27" s="3">
-        <v>2328900</v>
+        <v>2376500</v>
       </c>
       <c r="G27" s="3">
-        <v>1666600</v>
+        <v>1700600</v>
       </c>
       <c r="H27" s="3">
-        <v>1834100</v>
+        <v>1871500</v>
       </c>
       <c r="I27" s="3">
-        <v>1145500</v>
+        <v>1168900</v>
       </c>
       <c r="J27" s="3">
-        <v>1594700</v>
+        <v>1627200</v>
       </c>
       <c r="K27" s="3">
         <v>1649600</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>86300</v>
+        <v>88100</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -1602,13 +1602,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>1100100</v>
+        <v>1122600</v>
       </c>
       <c r="I29" s="3">
-        <v>-295500</v>
+        <v>-301500</v>
       </c>
       <c r="J29" s="3">
-        <v>-115300</v>
+        <v>-117600</v>
       </c>
       <c r="K29" s="3">
         <v>-47300</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-961300</v>
+        <v>-980900</v>
       </c>
       <c r="E32" s="3">
-        <v>-736000</v>
+        <v>-751100</v>
       </c>
       <c r="F32" s="3">
-        <v>-676700</v>
+        <v>-690500</v>
       </c>
       <c r="G32" s="3">
-        <v>-157100</v>
+        <v>-160300</v>
       </c>
       <c r="H32" s="3">
-        <v>-416100</v>
+        <v>-424600</v>
       </c>
       <c r="I32" s="3">
-        <v>-195500</v>
+        <v>-199500</v>
       </c>
       <c r="J32" s="3">
-        <v>-129400</v>
+        <v>-132100</v>
       </c>
       <c r="K32" s="3">
         <v>-179100</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4064200</v>
+        <v>4147100</v>
       </c>
       <c r="E33" s="3">
-        <v>2809800</v>
+        <v>2867200</v>
       </c>
       <c r="F33" s="3">
-        <v>2328900</v>
+        <v>2376500</v>
       </c>
       <c r="G33" s="3">
-        <v>1666600</v>
+        <v>1700600</v>
       </c>
       <c r="H33" s="3">
-        <v>2934200</v>
+        <v>2994100</v>
       </c>
       <c r="I33" s="3">
-        <v>850000</v>
+        <v>867400</v>
       </c>
       <c r="J33" s="3">
-        <v>1479400</v>
+        <v>1509600</v>
       </c>
       <c r="K33" s="3">
         <v>1602400</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4064200</v>
+        <v>4147100</v>
       </c>
       <c r="E35" s="3">
-        <v>2809800</v>
+        <v>2867200</v>
       </c>
       <c r="F35" s="3">
-        <v>2328900</v>
+        <v>2376500</v>
       </c>
       <c r="G35" s="3">
-        <v>1666600</v>
+        <v>1700600</v>
       </c>
       <c r="H35" s="3">
-        <v>2934200</v>
+        <v>2994100</v>
       </c>
       <c r="I35" s="3">
-        <v>850000</v>
+        <v>867400</v>
       </c>
       <c r="J35" s="3">
-        <v>1479400</v>
+        <v>1509600</v>
       </c>
       <c r="K35" s="3">
         <v>1602400</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2960600</v>
+        <v>3021000</v>
       </c>
       <c r="E41" s="3">
-        <v>3438700</v>
+        <v>3508900</v>
       </c>
       <c r="F41" s="3">
-        <v>2003100</v>
+        <v>2044000</v>
       </c>
       <c r="G41" s="3">
-        <v>1259600</v>
+        <v>1285300</v>
       </c>
       <c r="H41" s="3">
-        <v>448500</v>
+        <v>457700</v>
       </c>
       <c r="I41" s="3">
-        <v>689200</v>
+        <v>703300</v>
       </c>
       <c r="J41" s="3">
-        <v>381900</v>
+        <v>389700</v>
       </c>
       <c r="K41" s="3">
         <v>751100</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>14547200</v>
+        <v>14844100</v>
       </c>
       <c r="E42" s="3">
-        <v>12789500</v>
+        <v>13050600</v>
       </c>
       <c r="F42" s="3">
-        <v>11472300</v>
+        <v>11706500</v>
       </c>
       <c r="G42" s="3">
-        <v>11654100</v>
+        <v>11892000</v>
       </c>
       <c r="H42" s="3">
-        <v>9505400</v>
+        <v>9699400</v>
       </c>
       <c r="I42" s="3">
-        <v>6158500</v>
+        <v>6284200</v>
       </c>
       <c r="J42" s="3">
-        <v>5574200</v>
+        <v>5688000</v>
       </c>
       <c r="K42" s="3">
         <v>4272600</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1283800</v>
+        <v>1310000</v>
       </c>
       <c r="E43" s="3">
-        <v>900800</v>
+        <v>919200</v>
       </c>
       <c r="F43" s="3">
-        <v>985300</v>
+        <v>1005400</v>
       </c>
       <c r="G43" s="3">
-        <v>925700</v>
+        <v>944500</v>
       </c>
       <c r="H43" s="3">
-        <v>662400</v>
+        <v>675900</v>
       </c>
       <c r="I43" s="3">
-        <v>1241100</v>
+        <v>1266400</v>
       </c>
       <c r="J43" s="3">
-        <v>569700</v>
+        <v>581300</v>
       </c>
       <c r="K43" s="3">
         <v>1225200</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>96100</v>
+        <v>98000</v>
       </c>
       <c r="E44" s="3">
-        <v>137300</v>
+        <v>140100</v>
       </c>
       <c r="F44" s="3">
-        <v>133300</v>
+        <v>136000</v>
       </c>
       <c r="G44" s="3">
-        <v>85800</v>
+        <v>87600</v>
       </c>
       <c r="H44" s="3">
-        <v>89900</v>
+        <v>91700</v>
       </c>
       <c r="I44" s="3">
-        <v>147200</v>
+        <v>150200</v>
       </c>
       <c r="J44" s="3">
-        <v>756400</v>
+        <v>771900</v>
       </c>
       <c r="K44" s="3">
         <v>217900</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>826800</v>
+        <v>843600</v>
       </c>
       <c r="E45" s="3">
-        <v>916000</v>
+        <v>934700</v>
       </c>
       <c r="F45" s="3">
-        <v>1034700</v>
+        <v>1055900</v>
       </c>
       <c r="G45" s="3">
-        <v>972700</v>
+        <v>992600</v>
       </c>
       <c r="H45" s="3">
-        <v>1051900</v>
+        <v>1073400</v>
       </c>
       <c r="I45" s="3">
-        <v>2489700</v>
+        <v>2540500</v>
       </c>
       <c r="J45" s="3">
-        <v>1276500</v>
+        <v>1302600</v>
       </c>
       <c r="K45" s="3">
         <v>1741600</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>19714400</v>
+        <v>20116800</v>
       </c>
       <c r="E46" s="3">
-        <v>18182300</v>
+        <v>18553400</v>
       </c>
       <c r="F46" s="3">
-        <v>15628700</v>
+        <v>15947700</v>
       </c>
       <c r="G46" s="3">
-        <v>14897900</v>
+        <v>15202000</v>
       </c>
       <c r="H46" s="3">
-        <v>11758100</v>
+        <v>11998100</v>
       </c>
       <c r="I46" s="3">
-        <v>9493800</v>
+        <v>9687500</v>
       </c>
       <c r="J46" s="3">
-        <v>8558700</v>
+        <v>8733400</v>
       </c>
       <c r="K46" s="3">
         <v>6818900</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3367200</v>
+        <v>3435900</v>
       </c>
       <c r="E47" s="3">
-        <v>3213200</v>
+        <v>3278800</v>
       </c>
       <c r="F47" s="3">
-        <v>3424400</v>
+        <v>3494300</v>
       </c>
       <c r="G47" s="3">
-        <v>2561400</v>
+        <v>2613600</v>
       </c>
       <c r="H47" s="3">
-        <v>1831100</v>
+        <v>1868500</v>
       </c>
       <c r="I47" s="3">
-        <v>738600</v>
+        <v>753700</v>
       </c>
       <c r="J47" s="3">
-        <v>384700</v>
+        <v>392600</v>
       </c>
       <c r="K47" s="3">
         <v>348000</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1219200</v>
+        <v>1244100</v>
       </c>
       <c r="E48" s="3">
-        <v>998900</v>
+        <v>1019300</v>
       </c>
       <c r="F48" s="3">
-        <v>895000</v>
+        <v>913300</v>
       </c>
       <c r="G48" s="3">
-        <v>736200</v>
+        <v>751200</v>
       </c>
       <c r="H48" s="3">
-        <v>702600</v>
+        <v>716900</v>
       </c>
       <c r="I48" s="3">
-        <v>1388700</v>
+        <v>1417100</v>
       </c>
       <c r="J48" s="3">
-        <v>520800</v>
+        <v>531400</v>
       </c>
       <c r="K48" s="3">
         <v>668200</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>516700</v>
+        <v>527300</v>
       </c>
       <c r="E49" s="3">
-        <v>591900</v>
+        <v>604000</v>
       </c>
       <c r="F49" s="3">
-        <v>443800</v>
+        <v>452900</v>
       </c>
       <c r="G49" s="3">
-        <v>614000</v>
+        <v>626600</v>
       </c>
       <c r="H49" s="3">
-        <v>502800</v>
+        <v>513100</v>
       </c>
       <c r="I49" s="3">
-        <v>340600</v>
+        <v>347500</v>
       </c>
       <c r="J49" s="3">
-        <v>113300</v>
+        <v>115700</v>
       </c>
       <c r="K49" s="3">
         <v>35100</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>869900</v>
+        <v>887700</v>
       </c>
       <c r="E52" s="3">
-        <v>882300</v>
+        <v>900300</v>
       </c>
       <c r="F52" s="3">
-        <v>835500</v>
+        <v>852600</v>
       </c>
       <c r="G52" s="3">
-        <v>791900</v>
+        <v>808000</v>
       </c>
       <c r="H52" s="3">
-        <v>696500</v>
+        <v>710700</v>
       </c>
       <c r="I52" s="3">
-        <v>1930800</v>
+        <v>1970200</v>
       </c>
       <c r="J52" s="3">
-        <v>236100</v>
+        <v>241000</v>
       </c>
       <c r="K52" s="3">
         <v>818100</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>25687400</v>
+        <v>26211700</v>
       </c>
       <c r="E54" s="3">
-        <v>23868700</v>
+        <v>24355800</v>
       </c>
       <c r="F54" s="3">
-        <v>21227400</v>
+        <v>21660700</v>
       </c>
       <c r="G54" s="3">
-        <v>19601400</v>
+        <v>20001500</v>
       </c>
       <c r="H54" s="3">
-        <v>15491100</v>
+        <v>15807300</v>
       </c>
       <c r="I54" s="3">
-        <v>12015500</v>
+        <v>12260700</v>
       </c>
       <c r="J54" s="3">
-        <v>9813700</v>
+        <v>10014000</v>
       </c>
       <c r="K54" s="3">
         <v>8013000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>121700</v>
+        <v>124200</v>
       </c>
       <c r="E57" s="3">
-        <v>208200</v>
+        <v>212500</v>
       </c>
       <c r="F57" s="3">
-        <v>136100</v>
+        <v>138900</v>
       </c>
       <c r="G57" s="3">
-        <v>156700</v>
+        <v>159900</v>
       </c>
       <c r="H57" s="3">
-        <v>167500</v>
+        <v>170900</v>
       </c>
       <c r="I57" s="3">
-        <v>166000</v>
+        <v>169400</v>
       </c>
       <c r="J57" s="3">
-        <v>337500</v>
+        <v>344300</v>
       </c>
       <c r="K57" s="3">
         <v>192800</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2658200</v>
+        <v>2712500</v>
       </c>
       <c r="E58" s="3">
-        <v>3298700</v>
+        <v>3366000</v>
       </c>
       <c r="F58" s="3">
-        <v>2673700</v>
+        <v>2728300</v>
       </c>
       <c r="G58" s="3">
-        <v>2694800</v>
+        <v>2749800</v>
       </c>
       <c r="H58" s="3">
-        <v>2325000</v>
+        <v>2372400</v>
       </c>
       <c r="I58" s="3">
-        <v>1887100</v>
+        <v>1925600</v>
       </c>
       <c r="J58" s="3">
-        <v>915100</v>
+        <v>933800</v>
       </c>
       <c r="K58" s="3">
         <v>526900</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4658900</v>
+        <v>4754000</v>
       </c>
       <c r="E59" s="3">
-        <v>4344600</v>
+        <v>4433300</v>
       </c>
       <c r="F59" s="3">
-        <v>4167500</v>
+        <v>4252500</v>
       </c>
       <c r="G59" s="3">
-        <v>3606600</v>
+        <v>3680200</v>
       </c>
       <c r="H59" s="3">
-        <v>2791200</v>
+        <v>2848100</v>
       </c>
       <c r="I59" s="3">
-        <v>3605600</v>
+        <v>3679200</v>
       </c>
       <c r="J59" s="3">
-        <v>2028800</v>
+        <v>2070200</v>
       </c>
       <c r="K59" s="3">
         <v>2422300</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7438900</v>
+        <v>7590700</v>
       </c>
       <c r="E60" s="3">
-        <v>7851500</v>
+        <v>8011700</v>
       </c>
       <c r="F60" s="3">
-        <v>6977300</v>
+        <v>7119700</v>
       </c>
       <c r="G60" s="3">
-        <v>6458100</v>
+        <v>6589900</v>
       </c>
       <c r="H60" s="3">
-        <v>5283700</v>
+        <v>5391500</v>
       </c>
       <c r="I60" s="3">
-        <v>4850700</v>
+        <v>4949700</v>
       </c>
       <c r="J60" s="3">
-        <v>3281300</v>
+        <v>3348300</v>
       </c>
       <c r="K60" s="3">
         <v>2647900</v>
@@ -2841,13 +2841,13 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>59100</v>
+        <v>60300</v>
       </c>
       <c r="E61" s="3">
-        <v>505000</v>
+        <v>515300</v>
       </c>
       <c r="F61" s="3">
-        <v>176200</v>
+        <v>179800</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>493300</v>
+        <v>503400</v>
       </c>
       <c r="E62" s="3">
-        <v>470300</v>
+        <v>479900</v>
       </c>
       <c r="F62" s="3">
-        <v>337600</v>
+        <v>344500</v>
       </c>
       <c r="G62" s="3">
-        <v>184700</v>
+        <v>188500</v>
       </c>
       <c r="H62" s="3">
-        <v>115900</v>
+        <v>118300</v>
       </c>
       <c r="I62" s="3">
-        <v>61000</v>
+        <v>62200</v>
       </c>
       <c r="J62" s="3">
-        <v>32000</v>
+        <v>32600</v>
       </c>
       <c r="K62" s="3">
         <v>54200</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>8516100</v>
+        <v>8689900</v>
       </c>
       <c r="E66" s="3">
-        <v>9399000</v>
+        <v>9590800</v>
       </c>
       <c r="F66" s="3">
-        <v>8056900</v>
+        <v>8221400</v>
       </c>
       <c r="G66" s="3">
-        <v>8254800</v>
+        <v>8423200</v>
       </c>
       <c r="H66" s="3">
-        <v>7000700</v>
+        <v>7143600</v>
       </c>
       <c r="I66" s="3">
-        <v>5766300</v>
+        <v>5884000</v>
       </c>
       <c r="J66" s="3">
-        <v>3495400</v>
+        <v>3566700</v>
       </c>
       <c r="K66" s="3">
         <v>2739600</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>15716500</v>
+        <v>16037300</v>
       </c>
       <c r="E72" s="3">
-        <v>12759500</v>
+        <v>13020000</v>
       </c>
       <c r="F72" s="3">
-        <v>10878700</v>
+        <v>11100700</v>
       </c>
       <c r="G72" s="3">
-        <v>9034400</v>
+        <v>9218800</v>
       </c>
       <c r="H72" s="3">
-        <v>7959200</v>
+        <v>8121700</v>
       </c>
       <c r="I72" s="3">
-        <v>6246500</v>
+        <v>6374000</v>
       </c>
       <c r="J72" s="3">
-        <v>6070700</v>
+        <v>6194600</v>
       </c>
       <c r="K72" s="3">
         <v>5038400</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>17171300</v>
+        <v>17521800</v>
       </c>
       <c r="E76" s="3">
-        <v>14469700</v>
+        <v>14765000</v>
       </c>
       <c r="F76" s="3">
-        <v>13170500</v>
+        <v>13439400</v>
       </c>
       <c r="G76" s="3">
-        <v>11346600</v>
+        <v>11578200</v>
       </c>
       <c r="H76" s="3">
-        <v>8490400</v>
+        <v>8663700</v>
       </c>
       <c r="I76" s="3">
-        <v>6249200</v>
+        <v>6376800</v>
       </c>
       <c r="J76" s="3">
-        <v>6318300</v>
+        <v>6447300</v>
       </c>
       <c r="K76" s="3">
         <v>5273400</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4064200</v>
+        <v>4147100</v>
       </c>
       <c r="E81" s="3">
-        <v>2809800</v>
+        <v>2867200</v>
       </c>
       <c r="F81" s="3">
-        <v>2328900</v>
+        <v>2376500</v>
       </c>
       <c r="G81" s="3">
-        <v>1666600</v>
+        <v>1700600</v>
       </c>
       <c r="H81" s="3">
-        <v>2934200</v>
+        <v>2994100</v>
       </c>
       <c r="I81" s="3">
-        <v>850000</v>
+        <v>867400</v>
       </c>
       <c r="J81" s="3">
-        <v>1479400</v>
+        <v>1509600</v>
       </c>
       <c r="K81" s="3">
         <v>1602400</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>422100</v>
+        <v>430700</v>
       </c>
       <c r="E83" s="3">
-        <v>394900</v>
+        <v>403000</v>
       </c>
       <c r="F83" s="3">
-        <v>452600</v>
+        <v>461800</v>
       </c>
       <c r="G83" s="3">
-        <v>477700</v>
+        <v>487500</v>
       </c>
       <c r="H83" s="3">
-        <v>361100</v>
+        <v>368500</v>
       </c>
       <c r="I83" s="3">
-        <v>287900</v>
+        <v>293700</v>
       </c>
       <c r="J83" s="3">
-        <v>110800</v>
+        <v>113000</v>
       </c>
       <c r="K83" s="3">
         <v>45200</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4881400</v>
+        <v>4981000</v>
       </c>
       <c r="E89" s="3">
-        <v>3828300</v>
+        <v>3906400</v>
       </c>
       <c r="F89" s="3">
-        <v>3443900</v>
+        <v>3514200</v>
       </c>
       <c r="G89" s="3">
-        <v>3438500</v>
+        <v>3508700</v>
       </c>
       <c r="H89" s="3">
-        <v>2378600</v>
+        <v>2427200</v>
       </c>
       <c r="I89" s="3">
-        <v>1853500</v>
+        <v>1891400</v>
       </c>
       <c r="J89" s="3">
-        <v>1642600</v>
+        <v>1676100</v>
       </c>
       <c r="K89" s="3">
         <v>2138600</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-318000</v>
+        <v>-324500</v>
       </c>
       <c r="E91" s="3">
-        <v>-290200</v>
+        <v>-296100</v>
       </c>
       <c r="F91" s="3">
-        <v>-221300</v>
+        <v>-225800</v>
       </c>
       <c r="G91" s="3">
-        <v>-145800</v>
+        <v>-148800</v>
       </c>
       <c r="H91" s="3">
-        <v>-167100</v>
+        <v>-170500</v>
       </c>
       <c r="I91" s="3">
-        <v>-349300</v>
+        <v>-356400</v>
       </c>
       <c r="J91" s="3">
-        <v>-254600</v>
+        <v>-259800</v>
       </c>
       <c r="K91" s="3">
         <v>-156800</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2354700</v>
+        <v>-2402800</v>
       </c>
       <c r="E94" s="3">
-        <v>-1018200</v>
+        <v>-1039000</v>
       </c>
       <c r="F94" s="3">
-        <v>-977900</v>
+        <v>-997900</v>
       </c>
       <c r="G94" s="3">
-        <v>-4033200</v>
+        <v>-4115500</v>
       </c>
       <c r="H94" s="3">
-        <v>-3058400</v>
+        <v>-3120800</v>
       </c>
       <c r="I94" s="3">
-        <v>-1874800</v>
+        <v>-1913000</v>
       </c>
       <c r="J94" s="3">
-        <v>-1776100</v>
+        <v>-1812300</v>
       </c>
       <c r="K94" s="3">
         <v>-1637800</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1107200</v>
+        <v>-1129800</v>
       </c>
       <c r="E96" s="3">
-        <v>-928900</v>
+        <v>-947900</v>
       </c>
       <c r="F96" s="3">
-        <v>-484700</v>
+        <v>-494600</v>
       </c>
       <c r="G96" s="3">
-        <v>-591400</v>
+        <v>-603500</v>
       </c>
       <c r="H96" s="3">
-        <v>-1221400</v>
+        <v>-1246400</v>
       </c>
       <c r="I96" s="3">
-        <v>-199000</v>
+        <v>-203000</v>
       </c>
       <c r="J96" s="3">
-        <v>-450100</v>
+        <v>-459300</v>
       </c>
       <c r="K96" s="3">
         <v>-351600</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2965900</v>
+        <v>-3026400</v>
       </c>
       <c r="E100" s="3">
-        <v>-1414400</v>
+        <v>-1443300</v>
       </c>
       <c r="F100" s="3">
-        <v>-1738800</v>
+        <v>-1774300</v>
       </c>
       <c r="G100" s="3">
-        <v>1369600</v>
+        <v>1397500</v>
       </c>
       <c r="H100" s="3">
-        <v>149600</v>
+        <v>152600</v>
       </c>
       <c r="I100" s="3">
-        <v>219300</v>
+        <v>223800</v>
       </c>
       <c r="J100" s="3">
-        <v>-180000</v>
+        <v>-183700</v>
       </c>
       <c r="K100" s="3">
         <v>-310800</v>
@@ -4452,22 +4452,22 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-28000</v>
+        <v>-28500</v>
       </c>
       <c r="E101" s="3">
-        <v>15300</v>
+        <v>15600</v>
       </c>
       <c r="F101" s="3">
-        <v>-7600</v>
+        <v>-7800</v>
       </c>
       <c r="G101" s="3">
-        <v>22400</v>
+        <v>22800</v>
       </c>
       <c r="H101" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="I101" s="3">
-        <v>11300</v>
+        <v>11500</v>
       </c>
       <c r="J101" s="3">
         <v>-1800</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-467200</v>
+        <v>-476700</v>
       </c>
       <c r="E102" s="3">
-        <v>1410900</v>
+        <v>1439700</v>
       </c>
       <c r="F102" s="3">
-        <v>719500</v>
+        <v>734200</v>
       </c>
       <c r="G102" s="3">
-        <v>797300</v>
+        <v>813600</v>
       </c>
       <c r="H102" s="3">
-        <v>-526200</v>
+        <v>-536900</v>
       </c>
       <c r="I102" s="3">
-        <v>209400</v>
+        <v>213600</v>
       </c>
       <c r="J102" s="3">
-        <v>-315200</v>
+        <v>-321600</v>
       </c>
       <c r="K102" s="3">
         <v>208300</v>

--- a/AAII_Financials/Yearly/NTES_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NTES_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>NTES</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14586900</v>
+        <v>14591700</v>
       </c>
       <c r="E8" s="3">
-        <v>13604000</v>
+        <v>13990600</v>
       </c>
       <c r="F8" s="3">
-        <v>12350700</v>
+        <v>13790600</v>
       </c>
       <c r="G8" s="3">
-        <v>10385600</v>
+        <v>11283800</v>
       </c>
       <c r="H8" s="3">
-        <v>8351800</v>
+        <v>8508100</v>
       </c>
       <c r="I8" s="3">
-        <v>7215200</v>
+        <v>7441200</v>
       </c>
       <c r="J8" s="3">
-        <v>6264800</v>
+        <v>6829500</v>
       </c>
       <c r="K8" s="3">
         <v>4693900</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>5696300</v>
+        <v>5698100</v>
       </c>
       <c r="E9" s="3">
-        <v>6165000</v>
+        <v>6340200</v>
       </c>
       <c r="F9" s="3">
-        <v>5728800</v>
+        <v>6396600</v>
       </c>
       <c r="G9" s="3">
-        <v>4889700</v>
+        <v>5312600</v>
       </c>
       <c r="H9" s="3">
-        <v>3903200</v>
+        <v>3976200</v>
       </c>
       <c r="I9" s="3">
-        <v>3359900</v>
+        <v>3465200</v>
       </c>
       <c r="J9" s="3">
-        <v>2734200</v>
+        <v>2980700</v>
       </c>
       <c r="K9" s="3">
         <v>4052500</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>8890700</v>
+        <v>8893600</v>
       </c>
       <c r="E10" s="3">
-        <v>7439000</v>
+        <v>7650400</v>
       </c>
       <c r="F10" s="3">
-        <v>6621900</v>
+        <v>7393900</v>
       </c>
       <c r="G10" s="3">
-        <v>5495900</v>
+        <v>5971200</v>
       </c>
       <c r="H10" s="3">
-        <v>4448700</v>
+        <v>4531900</v>
       </c>
       <c r="I10" s="3">
-        <v>3855300</v>
+        <v>3976100</v>
       </c>
       <c r="J10" s="3">
-        <v>3530600</v>
+        <v>3848800</v>
       </c>
       <c r="K10" s="3">
         <v>641400</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>2324000</v>
+        <v>2324800</v>
       </c>
       <c r="E12" s="3">
-        <v>2120200</v>
+        <v>2180500</v>
       </c>
       <c r="F12" s="3">
-        <v>1984400</v>
+        <v>2215800</v>
       </c>
       <c r="G12" s="3">
-        <v>1461900</v>
+        <v>1588300</v>
       </c>
       <c r="H12" s="3">
-        <v>1186100</v>
+        <v>1208300</v>
       </c>
       <c r="I12" s="3">
-        <v>1040200</v>
+        <v>1072800</v>
       </c>
       <c r="J12" s="3">
-        <v>586700</v>
+        <v>639600</v>
       </c>
       <c r="K12" s="3">
         <v>823900</v>
@@ -969,23 +969,23 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>-38700</v>
-      </c>
-      <c r="E14" s="3">
-        <v>7800</v>
-      </c>
-      <c r="F14" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G14" s="3">
-        <v>7800</v>
+      <c r="D14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>17</v>
+      <c r="I14" s="3">
+        <v>3300</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>17</v>
@@ -1015,25 +1015,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>430900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>414400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>515700</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>529600</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>375400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>299500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>121700</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>10641800</v>
+        <v>10684000</v>
       </c>
       <c r="E17" s="3">
-        <v>10844600</v>
+        <v>11144700</v>
       </c>
       <c r="F17" s="3">
-        <v>10038900</v>
+        <v>11206300</v>
       </c>
       <c r="G17" s="3">
-        <v>8343800</v>
+        <v>9056900</v>
       </c>
       <c r="H17" s="3">
-        <v>6407600</v>
+        <v>6527500</v>
       </c>
       <c r="I17" s="3">
-        <v>5808500</v>
+        <v>5990600</v>
       </c>
       <c r="J17" s="3">
-        <v>4432800</v>
+        <v>4832300</v>
       </c>
       <c r="K17" s="3">
         <v>2902700</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>3945100</v>
+        <v>3907700</v>
       </c>
       <c r="E18" s="3">
-        <v>2759400</v>
+        <v>2845900</v>
       </c>
       <c r="F18" s="3">
-        <v>2311800</v>
+        <v>2584300</v>
       </c>
       <c r="G18" s="3">
-        <v>2041800</v>
+        <v>2226900</v>
       </c>
       <c r="H18" s="3">
-        <v>1944200</v>
+        <v>1980600</v>
       </c>
       <c r="I18" s="3">
-        <v>1406600</v>
+        <v>1450700</v>
       </c>
       <c r="J18" s="3">
-        <v>1832000</v>
+        <v>1997200</v>
       </c>
       <c r="K18" s="3">
         <v>1791300</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>980900</v>
+        <v>-129800</v>
       </c>
       <c r="E20" s="3">
-        <v>751100</v>
+        <v>-350600</v>
       </c>
       <c r="F20" s="3">
-        <v>690500</v>
+        <v>-34600</v>
       </c>
       <c r="G20" s="3">
-        <v>160300</v>
+        <v>363800</v>
       </c>
       <c r="H20" s="3">
-        <v>424600</v>
+        <v>-66700</v>
       </c>
       <c r="I20" s="3">
-        <v>199500</v>
+        <v>-77800</v>
       </c>
       <c r="J20" s="3">
-        <v>132100</v>
+        <v>28300</v>
       </c>
       <c r="K20" s="3">
         <v>179100</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>5355300</v>
+        <v>4468400</v>
       </c>
       <c r="E21" s="3">
-        <v>3912000</v>
+        <v>3610900</v>
       </c>
       <c r="F21" s="3">
-        <v>3462500</v>
+        <v>3134600</v>
       </c>
       <c r="G21" s="3">
-        <v>2687900</v>
+        <v>2392700</v>
       </c>
       <c r="H21" s="3">
-        <v>2736000</v>
+        <v>2422700</v>
       </c>
       <c r="I21" s="3">
-        <v>1898900</v>
+        <v>1828000</v>
       </c>
       <c r="J21" s="3">
-        <v>2076700</v>
+        <v>2090600</v>
       </c>
       <c r="K21" s="3">
         <v>2015600</v>
@@ -1275,25 +1275,25 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>124600</v>
+        <v>124700</v>
       </c>
       <c r="E22" s="3">
-        <v>91700</v>
-      </c>
-      <c r="F22" s="3">
-        <v>27000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>34900</v>
-      </c>
-      <c r="H22" s="3">
-        <v>59100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>44500</v>
-      </c>
-      <c r="J22" s="3">
-        <v>13000</v>
+        <v>94300</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K22" s="3">
         <v>4400</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4801300</v>
+        <v>4802900</v>
       </c>
       <c r="E23" s="3">
-        <v>3418800</v>
+        <v>3516000</v>
       </c>
       <c r="F23" s="3">
-        <v>2975300</v>
+        <v>3322200</v>
       </c>
       <c r="G23" s="3">
-        <v>2167200</v>
+        <v>2354600</v>
       </c>
       <c r="H23" s="3">
-        <v>2309700</v>
+        <v>2352900</v>
       </c>
       <c r="I23" s="3">
-        <v>1561600</v>
+        <v>1610500</v>
       </c>
       <c r="J23" s="3">
-        <v>1951100</v>
+        <v>2127000</v>
       </c>
       <c r="K23" s="3">
         <v>1965900</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>662600</v>
+        <v>662800</v>
       </c>
       <c r="E24" s="3">
-        <v>709400</v>
+        <v>729500</v>
       </c>
       <c r="F24" s="3">
-        <v>582000</v>
+        <v>649900</v>
       </c>
       <c r="G24" s="3">
-        <v>428800</v>
+        <v>465900</v>
       </c>
       <c r="H24" s="3">
-        <v>410900</v>
+        <v>418600</v>
       </c>
       <c r="I24" s="3">
-        <v>346900</v>
+        <v>357800</v>
       </c>
       <c r="J24" s="3">
-        <v>304000</v>
+        <v>331300</v>
       </c>
       <c r="K24" s="3">
         <v>290300</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4138800</v>
+        <v>4140100</v>
       </c>
       <c r="E26" s="3">
-        <v>2709400</v>
+        <v>2786400</v>
       </c>
       <c r="F26" s="3">
-        <v>2393300</v>
+        <v>2672300</v>
       </c>
       <c r="G26" s="3">
-        <v>1738300</v>
+        <v>1888600</v>
       </c>
       <c r="H26" s="3">
-        <v>1898800</v>
+        <v>1934300</v>
       </c>
       <c r="I26" s="3">
-        <v>1214700</v>
+        <v>1252800</v>
       </c>
       <c r="J26" s="3">
-        <v>1647200</v>
+        <v>1795600</v>
       </c>
       <c r="K26" s="3">
         <v>1675700</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4147100</v>
+        <v>4148500</v>
       </c>
       <c r="E27" s="3">
-        <v>2779100</v>
+        <v>2948700</v>
       </c>
       <c r="F27" s="3">
-        <v>2376500</v>
+        <v>2653500</v>
       </c>
       <c r="G27" s="3">
-        <v>1700600</v>
+        <v>1847700</v>
       </c>
       <c r="H27" s="3">
-        <v>1871500</v>
+        <v>3050100</v>
       </c>
       <c r="I27" s="3">
-        <v>1168900</v>
+        <v>894500</v>
       </c>
       <c r="J27" s="3">
-        <v>1627200</v>
+        <v>1645700</v>
       </c>
       <c r="K27" s="3">
         <v>1649600</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>88100</v>
+        <v>90600</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -1602,13 +1602,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>1122600</v>
+        <v>1143600</v>
       </c>
       <c r="I29" s="3">
-        <v>-301500</v>
+        <v>-311000</v>
       </c>
       <c r="J29" s="3">
-        <v>-117600</v>
+        <v>-128200</v>
       </c>
       <c r="K29" s="3">
         <v>-47300</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-980900</v>
+        <v>129800</v>
       </c>
       <c r="E32" s="3">
-        <v>-751100</v>
+        <v>350600</v>
       </c>
       <c r="F32" s="3">
-        <v>-690500</v>
+        <v>34600</v>
       </c>
       <c r="G32" s="3">
-        <v>-160300</v>
+        <v>-363800</v>
       </c>
       <c r="H32" s="3">
-        <v>-424600</v>
+        <v>66700</v>
       </c>
       <c r="I32" s="3">
-        <v>-199500</v>
+        <v>77800</v>
       </c>
       <c r="J32" s="3">
-        <v>-132100</v>
+        <v>-28300</v>
       </c>
       <c r="K32" s="3">
         <v>-179100</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4147100</v>
+        <v>4148500</v>
       </c>
       <c r="E33" s="3">
-        <v>2867200</v>
+        <v>2948700</v>
       </c>
       <c r="F33" s="3">
-        <v>2376500</v>
+        <v>2653500</v>
       </c>
       <c r="G33" s="3">
-        <v>1700600</v>
+        <v>1847700</v>
       </c>
       <c r="H33" s="3">
-        <v>2994100</v>
+        <v>3050100</v>
       </c>
       <c r="I33" s="3">
-        <v>867400</v>
+        <v>894500</v>
       </c>
       <c r="J33" s="3">
-        <v>1509600</v>
+        <v>1645700</v>
       </c>
       <c r="K33" s="3">
         <v>1602400</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4147100</v>
+        <v>4148500</v>
       </c>
       <c r="E35" s="3">
-        <v>2867200</v>
+        <v>2948700</v>
       </c>
       <c r="F35" s="3">
-        <v>2376500</v>
+        <v>2653500</v>
       </c>
       <c r="G35" s="3">
-        <v>1700600</v>
+        <v>1847700</v>
       </c>
       <c r="H35" s="3">
-        <v>2994100</v>
+        <v>3050100</v>
       </c>
       <c r="I35" s="3">
-        <v>867400</v>
+        <v>894500</v>
       </c>
       <c r="J35" s="3">
-        <v>1509600</v>
+        <v>1645700</v>
       </c>
       <c r="K35" s="3">
         <v>1602400</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3021000</v>
+        <v>3022000</v>
       </c>
       <c r="E41" s="3">
-        <v>3508900</v>
+        <v>3608600</v>
       </c>
       <c r="F41" s="3">
-        <v>2044000</v>
+        <v>2282200</v>
       </c>
       <c r="G41" s="3">
-        <v>1285300</v>
+        <v>1396500</v>
       </c>
       <c r="H41" s="3">
-        <v>457700</v>
+        <v>466200</v>
       </c>
       <c r="I41" s="3">
-        <v>703300</v>
+        <v>723700</v>
       </c>
       <c r="J41" s="3">
-        <v>389700</v>
+        <v>424800</v>
       </c>
       <c r="K41" s="3">
         <v>751100</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>14844100</v>
+        <v>14860400</v>
       </c>
       <c r="E42" s="3">
-        <v>13050600</v>
+        <v>13431300</v>
       </c>
       <c r="F42" s="3">
-        <v>11706500</v>
+        <v>13084900</v>
       </c>
       <c r="G42" s="3">
-        <v>11892000</v>
+        <v>12930100</v>
       </c>
       <c r="H42" s="3">
-        <v>9699400</v>
+        <v>9882600</v>
       </c>
       <c r="I42" s="3">
-        <v>6284200</v>
+        <v>6496700</v>
       </c>
       <c r="J42" s="3">
-        <v>5688000</v>
+        <v>6222000</v>
       </c>
       <c r="K42" s="3">
         <v>4272600</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1310000</v>
+        <v>1304800</v>
       </c>
       <c r="E43" s="3">
-        <v>919200</v>
+        <v>934100</v>
       </c>
       <c r="F43" s="3">
-        <v>1005400</v>
+        <v>1111900</v>
       </c>
       <c r="G43" s="3">
-        <v>944500</v>
+        <v>1014800</v>
       </c>
       <c r="H43" s="3">
-        <v>675900</v>
+        <v>677100</v>
       </c>
       <c r="I43" s="3">
-        <v>1266400</v>
+        <v>659100</v>
       </c>
       <c r="J43" s="3">
-        <v>581300</v>
+        <v>625200</v>
       </c>
       <c r="K43" s="3">
         <v>1225200</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>98000</v>
+        <v>98100</v>
       </c>
       <c r="E44" s="3">
-        <v>140100</v>
+        <v>144100</v>
       </c>
       <c r="F44" s="3">
-        <v>136000</v>
+        <v>151900</v>
       </c>
       <c r="G44" s="3">
-        <v>87600</v>
+        <v>90600</v>
       </c>
       <c r="H44" s="3">
-        <v>91700</v>
+        <v>93400</v>
       </c>
       <c r="I44" s="3">
-        <v>150200</v>
+        <v>154900</v>
       </c>
       <c r="J44" s="3">
-        <v>771900</v>
+        <v>841400</v>
       </c>
       <c r="K44" s="3">
         <v>217900</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>843600</v>
+        <v>30400</v>
       </c>
       <c r="E45" s="3">
-        <v>934700</v>
+        <v>135500</v>
       </c>
       <c r="F45" s="3">
-        <v>1055900</v>
+        <v>102100</v>
       </c>
       <c r="G45" s="3">
-        <v>992600</v>
+        <v>97300</v>
       </c>
       <c r="H45" s="3">
-        <v>1073400</v>
+        <v>122300</v>
       </c>
       <c r="I45" s="3">
-        <v>2540500</v>
+        <v>841400</v>
       </c>
       <c r="J45" s="3">
-        <v>1302600</v>
+        <v>102800</v>
       </c>
       <c r="K45" s="3">
         <v>1741600</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>20116800</v>
+        <v>20123300</v>
       </c>
       <c r="E46" s="3">
-        <v>18553400</v>
+        <v>19080700</v>
       </c>
       <c r="F46" s="3">
-        <v>15947700</v>
+        <v>17806900</v>
       </c>
       <c r="G46" s="3">
-        <v>15202000</v>
+        <v>16516700</v>
       </c>
       <c r="H46" s="3">
-        <v>11998100</v>
+        <v>12222600</v>
       </c>
       <c r="I46" s="3">
-        <v>9687500</v>
+        <v>9991100</v>
       </c>
       <c r="J46" s="3">
-        <v>8733400</v>
+        <v>9520600</v>
       </c>
       <c r="K46" s="3">
         <v>6818900</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3435900</v>
+        <v>3220100</v>
       </c>
       <c r="E47" s="3">
-        <v>3278800</v>
+        <v>3119800</v>
       </c>
       <c r="F47" s="3">
-        <v>3494300</v>
+        <v>3877000</v>
       </c>
       <c r="G47" s="3">
-        <v>2613600</v>
+        <v>2809400</v>
       </c>
       <c r="H47" s="3">
-        <v>1868500</v>
+        <v>1673700</v>
       </c>
       <c r="I47" s="3">
-        <v>753700</v>
+        <v>777200</v>
       </c>
       <c r="J47" s="3">
-        <v>392600</v>
+        <v>428000</v>
       </c>
       <c r="K47" s="3">
         <v>348000</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1244100</v>
+        <v>1244500</v>
       </c>
       <c r="E48" s="3">
-        <v>1019300</v>
+        <v>1048300</v>
       </c>
       <c r="F48" s="3">
-        <v>913300</v>
+        <v>1019700</v>
       </c>
       <c r="G48" s="3">
-        <v>751200</v>
+        <v>815400</v>
       </c>
       <c r="H48" s="3">
-        <v>716900</v>
+        <v>730400</v>
       </c>
       <c r="I48" s="3">
-        <v>1417100</v>
+        <v>679300</v>
       </c>
       <c r="J48" s="3">
-        <v>531400</v>
+        <v>579300</v>
       </c>
       <c r="K48" s="3">
         <v>668200</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>527300</v>
+        <v>1102100</v>
       </c>
       <c r="E49" s="3">
-        <v>604000</v>
+        <v>1218700</v>
       </c>
       <c r="F49" s="3">
-        <v>452900</v>
+        <v>1152400</v>
       </c>
       <c r="G49" s="3">
-        <v>626600</v>
+        <v>1320700</v>
       </c>
       <c r="H49" s="3">
-        <v>513100</v>
+        <v>1055100</v>
       </c>
       <c r="I49" s="3">
-        <v>347500</v>
+        <v>833500</v>
       </c>
       <c r="J49" s="3">
-        <v>115700</v>
+        <v>217300</v>
       </c>
       <c r="K49" s="3">
         <v>35100</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>887700</v>
+        <v>305300</v>
       </c>
       <c r="E52" s="3">
-        <v>900300</v>
+        <v>360000</v>
       </c>
       <c r="F52" s="3">
-        <v>852600</v>
+        <v>117000</v>
       </c>
       <c r="G52" s="3">
-        <v>808000</v>
+        <v>92900</v>
       </c>
       <c r="H52" s="3">
-        <v>710700</v>
+        <v>281200</v>
       </c>
       <c r="I52" s="3">
-        <v>1970200</v>
+        <v>194800</v>
       </c>
       <c r="J52" s="3">
-        <v>241000</v>
+        <v>28500</v>
       </c>
       <c r="K52" s="3">
         <v>818100</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>26211700</v>
+        <v>26220200</v>
       </c>
       <c r="E54" s="3">
-        <v>24355800</v>
+        <v>25048000</v>
       </c>
       <c r="F54" s="3">
-        <v>21660700</v>
+        <v>24186000</v>
       </c>
       <c r="G54" s="3">
-        <v>20001500</v>
+        <v>21731200</v>
       </c>
       <c r="H54" s="3">
-        <v>15807300</v>
+        <v>16103100</v>
       </c>
       <c r="I54" s="3">
-        <v>12260700</v>
+        <v>12644900</v>
       </c>
       <c r="J54" s="3">
-        <v>10014000</v>
+        <v>10916700</v>
       </c>
       <c r="K54" s="3">
         <v>8013000</v>
@@ -2664,22 +2664,22 @@
         <v>124200</v>
       </c>
       <c r="E57" s="3">
-        <v>212500</v>
+        <v>218500</v>
       </c>
       <c r="F57" s="3">
-        <v>138900</v>
+        <v>155100</v>
       </c>
       <c r="G57" s="3">
-        <v>159900</v>
+        <v>173800</v>
       </c>
       <c r="H57" s="3">
-        <v>170900</v>
+        <v>174100</v>
       </c>
       <c r="I57" s="3">
-        <v>169400</v>
+        <v>174700</v>
       </c>
       <c r="J57" s="3">
-        <v>344300</v>
+        <v>375400</v>
       </c>
       <c r="K57" s="3">
         <v>192800</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2712500</v>
+        <v>2750000</v>
       </c>
       <c r="E58" s="3">
-        <v>3366000</v>
+        <v>3499200</v>
       </c>
       <c r="F58" s="3">
-        <v>2728300</v>
+        <v>3099000</v>
       </c>
       <c r="G58" s="3">
-        <v>2749800</v>
+        <v>3038300</v>
       </c>
       <c r="H58" s="3">
-        <v>2372400</v>
+        <v>2444300</v>
       </c>
       <c r="I58" s="3">
-        <v>1925600</v>
+        <v>1985900</v>
       </c>
       <c r="J58" s="3">
-        <v>933800</v>
+        <v>1018000</v>
       </c>
       <c r="K58" s="3">
         <v>526900</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4754000</v>
+        <v>3128900</v>
       </c>
       <c r="E59" s="3">
-        <v>4433300</v>
+        <v>3037900</v>
       </c>
       <c r="F59" s="3">
-        <v>4252500</v>
+        <v>3278900</v>
       </c>
       <c r="G59" s="3">
-        <v>3680200</v>
+        <v>2717900</v>
       </c>
       <c r="H59" s="3">
-        <v>2848100</v>
+        <v>2003800</v>
       </c>
       <c r="I59" s="3">
-        <v>3679200</v>
+        <v>2098900</v>
       </c>
       <c r="J59" s="3">
-        <v>2070200</v>
+        <v>1522200</v>
       </c>
       <c r="K59" s="3">
         <v>2422300</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7590700</v>
+        <v>7593200</v>
       </c>
       <c r="E60" s="3">
-        <v>8011700</v>
+        <v>8239400</v>
       </c>
       <c r="F60" s="3">
-        <v>7119700</v>
+        <v>7949700</v>
       </c>
       <c r="G60" s="3">
-        <v>6589900</v>
+        <v>7159800</v>
       </c>
       <c r="H60" s="3">
-        <v>5391500</v>
+        <v>5492400</v>
       </c>
       <c r="I60" s="3">
-        <v>4949700</v>
+        <v>5104800</v>
       </c>
       <c r="J60" s="3">
-        <v>3348300</v>
+        <v>3650100</v>
       </c>
       <c r="K60" s="3">
         <v>2647900</v>
@@ -2841,19 +2841,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>60300</v>
+        <v>138700</v>
       </c>
       <c r="E61" s="3">
-        <v>515300</v>
+        <v>627400</v>
       </c>
       <c r="F61" s="3">
-        <v>179800</v>
+        <v>316000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>72700</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>40200</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>503400</v>
+        <v>100900</v>
       </c>
       <c r="E62" s="3">
-        <v>479900</v>
+        <v>87700</v>
       </c>
       <c r="F62" s="3">
-        <v>344500</v>
+        <v>57500</v>
       </c>
       <c r="G62" s="3">
-        <v>188500</v>
+        <v>22800</v>
       </c>
       <c r="H62" s="3">
-        <v>118300</v>
+        <v>25600</v>
       </c>
       <c r="I62" s="3">
-        <v>62200</v>
+        <v>8000</v>
       </c>
       <c r="J62" s="3">
-        <v>32600</v>
+        <v>2800</v>
       </c>
       <c r="K62" s="3">
         <v>54200</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>8689900</v>
+        <v>8157100</v>
       </c>
       <c r="E66" s="3">
-        <v>9590800</v>
+        <v>9262800</v>
       </c>
       <c r="F66" s="3">
-        <v>8221400</v>
+        <v>8535100</v>
       </c>
       <c r="G66" s="3">
-        <v>8423200</v>
+        <v>7364600</v>
       </c>
       <c r="H66" s="3">
-        <v>7143600</v>
+        <v>5613000</v>
       </c>
       <c r="I66" s="3">
-        <v>5884000</v>
+        <v>5169800</v>
       </c>
       <c r="J66" s="3">
-        <v>3566700</v>
+        <v>3685700</v>
       </c>
       <c r="K66" s="3">
         <v>2739600</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>16037300</v>
+        <v>16042500</v>
       </c>
       <c r="E72" s="3">
-        <v>13020000</v>
+        <v>13390000</v>
       </c>
       <c r="F72" s="3">
-        <v>11100700</v>
+        <v>12394900</v>
       </c>
       <c r="G72" s="3">
-        <v>9218800</v>
+        <v>10016100</v>
       </c>
       <c r="H72" s="3">
-        <v>8121700</v>
+        <v>8273700</v>
       </c>
       <c r="I72" s="3">
-        <v>6374000</v>
+        <v>6573700</v>
       </c>
       <c r="J72" s="3">
-        <v>6194600</v>
+        <v>6752900</v>
       </c>
       <c r="K72" s="3">
         <v>5038400</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>17521800</v>
+        <v>17527500</v>
       </c>
       <c r="E76" s="3">
-        <v>14765000</v>
+        <v>15184600</v>
       </c>
       <c r="F76" s="3">
-        <v>13439400</v>
+        <v>15006200</v>
       </c>
       <c r="G76" s="3">
-        <v>11578200</v>
+        <v>12579500</v>
       </c>
       <c r="H76" s="3">
-        <v>8663700</v>
+        <v>8825900</v>
       </c>
       <c r="I76" s="3">
-        <v>6376800</v>
+        <v>6576600</v>
       </c>
       <c r="J76" s="3">
-        <v>6447300</v>
+        <v>7028400</v>
       </c>
       <c r="K76" s="3">
         <v>5273400</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4147100</v>
+        <v>4148500</v>
       </c>
       <c r="E81" s="3">
-        <v>2867200</v>
+        <v>2948700</v>
       </c>
       <c r="F81" s="3">
-        <v>2376500</v>
+        <v>2653500</v>
       </c>
       <c r="G81" s="3">
-        <v>1700600</v>
+        <v>1847700</v>
       </c>
       <c r="H81" s="3">
-        <v>2994100</v>
+        <v>3050100</v>
       </c>
       <c r="I81" s="3">
-        <v>867400</v>
+        <v>894500</v>
       </c>
       <c r="J81" s="3">
-        <v>1509600</v>
+        <v>1645700</v>
       </c>
       <c r="K81" s="3">
         <v>1602400</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>430700</v>
+        <v>416500</v>
       </c>
       <c r="E83" s="3">
-        <v>403000</v>
+        <v>401100</v>
       </c>
       <c r="F83" s="3">
-        <v>461800</v>
+        <v>501900</v>
       </c>
       <c r="G83" s="3">
-        <v>487500</v>
+        <v>516700</v>
       </c>
       <c r="H83" s="3">
-        <v>368500</v>
+        <v>365000</v>
       </c>
       <c r="I83" s="3">
-        <v>293700</v>
+        <v>295000</v>
       </c>
       <c r="J83" s="3">
-        <v>113000</v>
+        <v>120300</v>
       </c>
       <c r="K83" s="3">
         <v>45200</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4981000</v>
+        <v>4982600</v>
       </c>
       <c r="E89" s="3">
-        <v>3906400</v>
+        <v>4017500</v>
       </c>
       <c r="F89" s="3">
-        <v>3514200</v>
+        <v>3923900</v>
       </c>
       <c r="G89" s="3">
-        <v>3508700</v>
+        <v>3812200</v>
       </c>
       <c r="H89" s="3">
-        <v>2427200</v>
+        <v>2472600</v>
       </c>
       <c r="I89" s="3">
-        <v>1891400</v>
+        <v>1950600</v>
       </c>
       <c r="J89" s="3">
-        <v>1676100</v>
+        <v>1827200</v>
       </c>
       <c r="K89" s="3">
         <v>2138600</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-324500</v>
+        <v>-324600</v>
       </c>
       <c r="E91" s="3">
-        <v>-296100</v>
+        <v>-304500</v>
       </c>
       <c r="F91" s="3">
-        <v>-225800</v>
+        <v>-252200</v>
       </c>
       <c r="G91" s="3">
-        <v>-148800</v>
+        <v>-161700</v>
       </c>
       <c r="H91" s="3">
-        <v>-170500</v>
+        <v>-173700</v>
       </c>
       <c r="I91" s="3">
-        <v>-356400</v>
+        <v>-315400</v>
       </c>
       <c r="J91" s="3">
-        <v>-259800</v>
+        <v>-254300</v>
       </c>
       <c r="K91" s="3">
         <v>-156800</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2402800</v>
+        <v>-2403600</v>
       </c>
       <c r="E94" s="3">
-        <v>-1039000</v>
+        <v>-1068500</v>
       </c>
       <c r="F94" s="3">
-        <v>-997900</v>
+        <v>-1114200</v>
       </c>
       <c r="G94" s="3">
-        <v>-4115500</v>
+        <v>-4471500</v>
       </c>
       <c r="H94" s="3">
-        <v>-3120800</v>
+        <v>-3179200</v>
       </c>
       <c r="I94" s="3">
-        <v>-1913000</v>
+        <v>-1973000</v>
       </c>
       <c r="J94" s="3">
-        <v>-1812300</v>
+        <v>-1975700</v>
       </c>
       <c r="K94" s="3">
         <v>-1637800</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1129800</v>
+        <v>1130200</v>
       </c>
       <c r="E96" s="3">
-        <v>-947900</v>
+        <v>974800</v>
       </c>
       <c r="F96" s="3">
-        <v>-494600</v>
+        <v>552300</v>
       </c>
       <c r="G96" s="3">
-        <v>-603500</v>
+        <v>655600</v>
       </c>
       <c r="H96" s="3">
-        <v>-1246400</v>
+        <v>1269700</v>
       </c>
       <c r="I96" s="3">
-        <v>-203000</v>
+        <v>209400</v>
       </c>
       <c r="J96" s="3">
-        <v>-459300</v>
+        <v>500700</v>
       </c>
       <c r="K96" s="3">
         <v>-351600</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-3026400</v>
+        <v>-3027400</v>
       </c>
       <c r="E100" s="3">
-        <v>-1443300</v>
+        <v>-1484300</v>
       </c>
       <c r="F100" s="3">
-        <v>-1774300</v>
+        <v>-1981200</v>
       </c>
       <c r="G100" s="3">
-        <v>1397500</v>
+        <v>1518400</v>
       </c>
       <c r="H100" s="3">
-        <v>152600</v>
+        <v>155500</v>
       </c>
       <c r="I100" s="3">
-        <v>223800</v>
+        <v>230800</v>
       </c>
       <c r="J100" s="3">
-        <v>-183700</v>
+        <v>-200200</v>
       </c>
       <c r="K100" s="3">
         <v>-310800</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-28500</v>
+        <v>-28600</v>
       </c>
       <c r="E101" s="3">
-        <v>15600</v>
+        <v>16000</v>
       </c>
       <c r="F101" s="3">
-        <v>-7800</v>
+        <v>-8700</v>
       </c>
       <c r="G101" s="3">
-        <v>22800</v>
+        <v>24800</v>
       </c>
       <c r="H101" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="I101" s="3">
-        <v>11500</v>
+        <v>11900</v>
       </c>
       <c r="J101" s="3">
-        <v>-1800</v>
+        <v>-2000</v>
       </c>
       <c r="K101" s="3">
         <v>18300</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-476700</v>
+        <v>-476900</v>
       </c>
       <c r="E102" s="3">
-        <v>1439700</v>
+        <v>1480600</v>
       </c>
       <c r="F102" s="3">
-        <v>734200</v>
+        <v>819700</v>
       </c>
       <c r="G102" s="3">
-        <v>813600</v>
+        <v>883900</v>
       </c>
       <c r="H102" s="3">
-        <v>-536900</v>
+        <v>-547000</v>
       </c>
       <c r="I102" s="3">
-        <v>213600</v>
+        <v>220300</v>
       </c>
       <c r="J102" s="3">
-        <v>-321600</v>
+        <v>-350600</v>
       </c>
       <c r="K102" s="3">
         <v>208300</v>

--- a/AAII_Financials/Yearly/NTES_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NTES_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>NTES</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>14425800</v>
+      </c>
+      <c r="E8" s="3">
         <v>14591700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13990600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13790600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11283800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8508100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7441200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6829500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4693900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3018900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1847800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1405000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1176700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1082000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5410000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5698100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6340200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6396600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5312600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3976200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3465200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2980700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4052500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2470500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>514500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>378700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>369900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>352100</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9015800</v>
+      </c>
+      <c r="E10" s="3">
         <v>8893600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7650400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7393900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5971200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4531900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3976100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3848800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>641400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>548400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1333300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1026300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>806800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>729900</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,53 +886,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2401000</v>
+      </c>
+      <c r="E12" s="3">
         <v>2324800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2180500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2215800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1588300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1208300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1072800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>639600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>823900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>595900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>208800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>140800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>103100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>69100</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,9 +979,12 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,11 +1003,11 @@
       <c r="H14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="3">
         <v>3300</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>17</v>
@@ -999,8 +1018,8 @@
       <c r="M14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1008,36 +1027,39 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>331300</v>
+      </c>
+      <c r="E15" s="3">
         <v>430900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>414400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>515700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>529600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>375400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>299500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>121700</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>10372700</v>
+      </c>
+      <c r="E17" s="3">
         <v>10684000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11144700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11206300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9056900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6527500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5990600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4832300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2902700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1979200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1096100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>740000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>644100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>588800</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>4053100</v>
+      </c>
+      <c r="E18" s="3">
         <v>3907700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2845900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2584300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2226900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1980600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1450700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1997200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1791300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1039700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>751700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>665000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>532500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>493200</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1179,109 +1211,116 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-117500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-129800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-350600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-34600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>363800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-66700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-77800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>28300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>179100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>119200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>112500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>97100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>81300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>43400</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>4501800</v>
+      </c>
+      <c r="E21" s="3">
         <v>4468400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3610900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3134600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2392700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2422700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1828000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2090600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2015600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1184100</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P21" s="3">
         <v>647300</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="3">
         <v>124700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>94300</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>17</v>
@@ -1295,117 +1334,126 @@
       <c r="J22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22" s="3">
         <v>4400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1900</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4893400</v>
+      </c>
+      <c r="E23" s="3">
         <v>4802900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3516000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3322200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2354600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2352900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1610500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2127000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1965900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1156200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>861100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>760200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>613800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>536600</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>748200</v>
+      </c>
+      <c r="E24" s="3">
         <v>662800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>729500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>649900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>465900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>418600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>357800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>331300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>290300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>175500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>104600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>81100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>99200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>58300</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4145200</v>
+      </c>
+      <c r="E26" s="3">
         <v>4140100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2786400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2672300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1888600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1934300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1252800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1795600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1675700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>980700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>756600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>679100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>514600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>478300</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4068700</v>
+      </c>
+      <c r="E27" s="3">
         <v>4148500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2948700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2653500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1847700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3050100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>894500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1645700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1649600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>966500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>750400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>678900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>521900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>480000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1593,44 +1653,47 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>90600</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>1143600</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-311000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-128200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-47300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-29000</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>117500</v>
+      </c>
+      <c r="E32" s="3">
         <v>129800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>350600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>34600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-363800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>66700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>77800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-28300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-179100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-119200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-112500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-97100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-81300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-43400</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4068700</v>
+      </c>
+      <c r="E33" s="3">
         <v>4148500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2948700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2653500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1847700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3050100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>894500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1645700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1602400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>937500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>750400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>678900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>521900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>480000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4068700</v>
+      </c>
+      <c r="E35" s="3">
         <v>4148500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2948700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2653500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1847700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3050100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>894500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1645700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1602400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>937500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>750400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>678900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>521900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>480000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,178 +2072,188 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7039700</v>
+      </c>
+      <c r="E41" s="3">
         <v>3022000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3608600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2282200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1396500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>466200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>723700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>424800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>751100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>845200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>957800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>222800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>228200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>328700</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>11809300</v>
+      </c>
+      <c r="E42" s="3">
         <v>14860400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>13431300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13084900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12930100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9882600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6496700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6222000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4272600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2729300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3093200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2677700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2033400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1587700</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>776700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1304800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>934100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1111900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1014800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>677100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>659100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>625200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1225200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>410000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>464700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>104500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>66300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>50800</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E44" s="3">
         <v>98100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>144100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>151900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>90600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>93400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>154900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>841400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>217900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>113800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>129000</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>17</v>
@@ -2166,234 +2261,252 @@
       <c r="P44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>879100</v>
+      </c>
+      <c r="E45" s="3">
         <v>30400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>135500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>102100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>97300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>122300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>841400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>102800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1741600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>691400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>783600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>478000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>235800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>180900</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>21006000</v>
+      </c>
+      <c r="E46" s="3">
         <v>20123300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19080700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17806900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16516700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12222600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9991100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9520600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6818900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4789700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5428400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3483000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2563800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2148100</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>414400</v>
+      </c>
+      <c r="E47" s="3">
         <v>3220100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3119800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3877000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2809400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1673700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>777200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>428000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>348000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>400200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>453500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>117000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>75200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1167300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1244500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1048300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1019700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>815400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>730400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>679300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>579300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>668200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>291200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>367700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>133200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>116900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>125900</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>571600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1102100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1218700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1152400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1320700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1055100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>833500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>217300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>35100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>26600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>30100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3539600</v>
+      </c>
+      <c r="E52" s="3">
         <v>305300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>360000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>117000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>92900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>281200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>194800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>28500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>818100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>221400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>213300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7900</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26851500</v>
+      </c>
+      <c r="E54" s="3">
         <v>26220200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>25048000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>24186000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21731200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16103100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12644900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10916700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8013000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5729100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6493000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3750200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2766000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2292200</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,209 +2784,222 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>98700</v>
+      </c>
+      <c r="E57" s="3">
         <v>124200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>218500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>155100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>173800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>174100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>174700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>375400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>192800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>97500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>110500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>33500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>22600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>19900</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1617300</v>
+      </c>
+      <c r="E58" s="3">
         <v>2750000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3499200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3099000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3038300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2444300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1985900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1018000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>526900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>316400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>358600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>149000</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2474100</v>
+      </c>
+      <c r="E59" s="3">
         <v>3128900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3037900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3278900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2717900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2003800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2098900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1522200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2422300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1210200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1371600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>464200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>490500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>318800</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6804600</v>
+      </c>
+      <c r="E60" s="3">
         <v>7593200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8239400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7949700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7159800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5492400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5104800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3650100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2647900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1624100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1840700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>646700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>513200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>338800</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E61" s="3">
         <v>138700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>627400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>316000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>72700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>40200</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2879,54 +3021,60 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>168300</v>
+      </c>
+      <c r="E62" s="3">
         <v>100900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>87700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>57500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>22800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>25600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>54200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>23200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>26300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>22100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9500</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7329300</v>
+      </c>
+      <c r="E66" s="3">
         <v>8157100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9262800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8535100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7364600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5613000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5169800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3685700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2739600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1658900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1880100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>657100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>516100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>344000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="3">
         <v>16042500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>13390000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12394900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10016100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8273700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6573700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6752900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5038400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3818300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4327500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2827800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2053100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1728800</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19000400</v>
+      </c>
+      <c r="E76" s="3">
         <v>17527500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15184600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15006200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12579500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8825900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6576600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7028400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5273400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4070200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4612900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3093100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2249900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1948100</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4068700</v>
+      </c>
+      <c r="E81" s="3">
         <v>4148500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2948700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2653500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1847700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3050100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>894500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1645700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1602400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>937500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>750400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>678900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>521900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>480000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>331300</v>
+      </c>
+      <c r="E83" s="3">
         <v>416500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>401100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>501900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>516700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>365000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>295000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>120300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>45200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>25400</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P83" s="3">
         <v>33500</v>
       </c>
-      <c r="P83" s="3" t="s">
+      <c r="Q83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5435900</v>
+      </c>
+      <c r="E89" s="3">
         <v>4982600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4017500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3923900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3812200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2472600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1950600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1827200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2138600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1124300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>926500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>799900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>606100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>604500</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-174700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-324600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-304500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-252200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-161700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-173700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-315400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-254300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-156800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-120600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-84800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-33400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-25600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-60900</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2454600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2403600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1068500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1114200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4471500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3179200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1973000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1975700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1637800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-353100</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P94" s="3">
         <v>-639100</v>
       </c>
-      <c r="P94" s="3" t="s">
+      <c r="Q94" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1529700</v>
+      </c>
+      <c r="E96" s="3">
         <v>1130200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>974800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>552300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>655600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1269700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>209400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>500700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-351600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-204300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-312800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-124600</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3745100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3027400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1484300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1981200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1518400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>155500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>230800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-200200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-310800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-227300</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P100" s="3">
         <v>-56000</v>
       </c>
-      <c r="P100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-28600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>16000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>24800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>11900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>18300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>19800</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3" t="s">
+      <c r="Q101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4146800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-476900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1480600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>819700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>883900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-547000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>220300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-350600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>208300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>563800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>88800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-20200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-89500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>137900</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NTES_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NTES_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>NTES</t>
   </si>
@@ -1313,14 +1313,14 @@
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>17</v>
+      <c r="D22" s="3">
+        <v>81900</v>
       </c>
       <c r="E22" s="3">
         <v>124700</v>
       </c>
-      <c r="F22" s="3">
-        <v>94300</v>
+      <c r="F22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>17</v>
@@ -2127,7 +2127,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>11809300</v>
+        <v>11821900</v>
       </c>
       <c r="E42" s="3">
         <v>14860400</v>
@@ -2175,7 +2175,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>776700</v>
+        <v>1117700</v>
       </c>
       <c r="E43" s="3">
         <v>1304800</v>
@@ -2271,7 +2271,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>879100</v>
+        <v>30800</v>
       </c>
       <c r="E45" s="3">
         <v>30400</v>
@@ -2367,7 +2367,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>414400</v>
+        <v>3182800</v>
       </c>
       <c r="E47" s="3">
         <v>3220100</v>
@@ -2415,7 +2415,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1167300</v>
+        <v>1241400</v>
       </c>
       <c r="E48" s="3">
         <v>1244500</v>
@@ -2463,7 +2463,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>571600</v>
+        <v>1019400</v>
       </c>
       <c r="E49" s="3">
         <v>1102100</v>
@@ -2607,7 +2607,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3539600</v>
+        <v>247000</v>
       </c>
       <c r="E52" s="3">
         <v>305300</v>
@@ -2839,7 +2839,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1617300</v>
+        <v>1640800</v>
       </c>
       <c r="E58" s="3">
         <v>2750000</v>
@@ -2887,7 +2887,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2474100</v>
+        <v>3413900</v>
       </c>
       <c r="E59" s="3">
         <v>3128900</v>
@@ -2983,7 +2983,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>58600</v>
+        <v>115200</v>
       </c>
       <c r="E61" s="3">
         <v>138700</v>
@@ -3031,7 +3031,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>168300</v>
+        <v>111800</v>
       </c>
       <c r="E62" s="3">
         <v>100900</v>
@@ -3482,8 +3482,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>17</v>
+      <c r="D72" s="3">
+        <v>18123900</v>
       </c>
       <c r="E72" s="3">
         <v>16042500</v>
@@ -3892,7 +3892,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>331300</v>
+        <v>315800</v>
       </c>
       <c r="E83" s="3">
         <v>416500</v>

--- a/AAII_Financials/Yearly/NTES_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NTES_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>NTES</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>16102300</v>
+      </c>
+      <c r="E8" s="3">
         <v>14425800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14591700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13990600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13790600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11283800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8508100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7441200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6829500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4693900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3018900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1847800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1405000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1176700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1082000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5750900</v>
+      </c>
+      <c r="E9" s="3">
         <v>5410000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5698100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6340200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6396600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5312600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3976200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3465200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2980700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4052500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2470500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>514500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>378700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>369900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>352100</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>10351400</v>
+      </c>
+      <c r="E10" s="3">
         <v>9015800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8893600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7650400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7393900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5971200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4531900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3976100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3848800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>641400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>548400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1333300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1026300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>806800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>729900</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,56 +899,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2533300</v>
+      </c>
+      <c r="E12" s="3">
         <v>2401000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2324800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2180500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2215800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1588300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1208300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1072800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>639600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>823900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>595900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>208800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>140800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>103100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>69100</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -982,9 +998,12 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,11 +1025,11 @@
       <c r="I14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" s="3">
         <v>3300</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>17</v>
@@ -1021,8 +1040,8 @@
       <c r="N14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1030,39 +1049,42 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>321300</v>
+      </c>
+      <c r="E15" s="3">
         <v>331300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>430900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>414400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>515700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>529600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>375400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>299500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>121700</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>10978900</v>
+      </c>
+      <c r="E17" s="3">
         <v>10372700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10684000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11144700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11206300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9056900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6527500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5990600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4832300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2902700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1979200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1096100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>740000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>644100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>588800</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>5123400</v>
+      </c>
+      <c r="E18" s="3">
         <v>4053100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3907700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2845900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2584300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2226900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1980600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1450700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1997200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1791300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1039700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>751700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>665000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>532500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>493200</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1212,112 +1244,119 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-44400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-117500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-129800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-350600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-34600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>363800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-66700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-77800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>28300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>179100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>119200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>112500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>97100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>81300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>43400</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>5489100</v>
+      </c>
+      <c r="E21" s="3">
         <v>4501800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4468400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3610900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3134600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2392700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2422700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1828000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2090600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2015600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1184100</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q21" s="3">
         <v>647300</v>
       </c>
-      <c r="Q21" s="3" t="s">
+      <c r="R21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E22" s="3">
         <v>81900</v>
-      </c>
-      <c r="E22" s="3">
-        <v>124700</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>17</v>
@@ -1337,123 +1376,132 @@
       <c r="K22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M22" s="3">
         <v>4400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1900</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5837600</v>
+      </c>
+      <c r="E23" s="3">
         <v>4893400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4802900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3516000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3322200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2354600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2352900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1610500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2127000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1965900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1156200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>861100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>760200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>613800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>536600</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>862500</v>
+      </c>
+      <c r="E24" s="3">
         <v>748200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>662800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>729500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>649900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>465900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>418600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>357800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>331300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>290300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>175500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>104600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>81100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>99200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>58300</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4975100</v>
+      </c>
+      <c r="E26" s="3">
         <v>4145200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4140100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2786400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2672300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1888600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1934300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1252800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1795600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1675700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>980700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>756600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>679100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>514600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>478300</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4826700</v>
+      </c>
+      <c r="E27" s="3">
         <v>4068700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4148500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2948700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2653500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1847700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3050100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>894500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1645700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1649600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>966500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>750400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>678900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>521900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>480000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1656,44 +1716,47 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>90600</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>1143600</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-311000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-128200</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-47300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-29000</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E32" s="3">
         <v>117500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>129800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>350600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>34600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-363800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>66700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>77800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-28300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-179100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-119200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-112500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-97100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-81300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-43400</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4826700</v>
+      </c>
+      <c r="E33" s="3">
         <v>4068700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4148500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2948700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2653500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1847700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3050100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>894500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1645700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1602400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>937500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>750400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>678900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>521900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>480000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4826700</v>
+      </c>
+      <c r="E35" s="3">
         <v>4068700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4148500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2948700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2653500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1847700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3050100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>894500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1645700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1602400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>937500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>750400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>678900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>521900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>480000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,190 +2158,200 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6743700</v>
+      </c>
+      <c r="E41" s="3">
         <v>7039700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3022000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3608600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2282200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1396500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>466200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>723700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>424800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>751100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>845200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>957800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>222800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>228200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>328700</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>16738000</v>
+      </c>
+      <c r="E42" s="3">
         <v>11821900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>14860400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13431300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>13084900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12930100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9882600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6496700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6222000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4272600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2729300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3093200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2677700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2033400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1587700</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1029200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1117700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1304800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>934100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1111900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1014800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>677100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>659100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>625200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1225200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>410000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>464700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>104500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>66300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>50800</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>98500</v>
+      </c>
+      <c r="E44" s="3">
         <v>78300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>98100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>144100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>151900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>90600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>93400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>154900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>841400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>217900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>113800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>129000</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>17</v>
@@ -2264,249 +2359,267 @@
       <c r="Q44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E45" s="3">
         <v>30800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>30400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>135500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>102100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>97300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>122300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>841400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>102800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1741600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>691400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>783600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>478000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>235800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>180900</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25822900</v>
+      </c>
+      <c r="E46" s="3">
         <v>21006000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20123300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19080700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17806900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16516700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12222600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9991100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9520600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6818900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4789700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5428400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3483000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2563800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2148100</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3067900</v>
+      </c>
+      <c r="E47" s="3">
         <v>3182800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3220100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3119800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3877000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2809400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1673700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>777200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>428000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>348000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>400200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>453500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>117000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>75200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1250400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1241400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1244500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1048300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1019700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>815400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>730400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>679300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>579300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>668200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>291200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>367700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>133200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>116900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>125900</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>979400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1019400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1102100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1218700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1152400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1320700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1055100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>833500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>217300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>35100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>26600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>30100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>128400</v>
+      </c>
+      <c r="E52" s="3">
         <v>247000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>305300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>360000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>117000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>92900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>281200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>194800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>818100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>221400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>213300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7900</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31656000</v>
+      </c>
+      <c r="E54" s="3">
         <v>26851500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>26220200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>25048000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>24186000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21731200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16103100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12644900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10916700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8013000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5729100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6493000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3750200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2766000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2292200</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,224 +2914,237 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E57" s="3">
         <v>98700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>124200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>218500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>155100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>173800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>174100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>174700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>375400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>192800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>97500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>110500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>33500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>22600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>19900</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>929000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1640800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2750000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3499200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3099000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3038300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2444300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1985900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1018000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>526900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>316400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>358600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>149000</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4704000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3413900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3128900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3037900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3278900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2717900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2003800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2098900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1522200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2422300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1210200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1371600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>464200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>490500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>318800</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7487300</v>
+      </c>
+      <c r="E60" s="3">
         <v>6804600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7593200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8239400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7949700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7159800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5492400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5104800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3650100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2647900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1624100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1840700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>646700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>513200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>338800</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E61" s="3">
         <v>115200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>138700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>627400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>316000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>72700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>40200</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -3024,57 +3166,63 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>153400</v>
+      </c>
+      <c r="E62" s="3">
         <v>111800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>100900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>87700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>57500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>22800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>25600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>54200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>26300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>22100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9500</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8050900</v>
+      </c>
+      <c r="E66" s="3">
         <v>7329300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8157100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9262800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8535100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7364600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5613000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5169800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3685700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2739600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1658900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1880100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>657100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>516100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>344000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>21762000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18123900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>16042500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>13390000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12394900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10016100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8273700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6573700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6752900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5038400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3818300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4327500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2827800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2053100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1728800</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22917800</v>
+      </c>
+      <c r="E76" s="3">
         <v>19000400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17527500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15184600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15006200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12579500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8825900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6576600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7028400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5273400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4070200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4612900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3093100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2249900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1948100</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4826700</v>
+      </c>
+      <c r="E81" s="3">
         <v>4068700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4148500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2948700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2653500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1847700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3050100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>894500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1645700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1602400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>937500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>750400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>678900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>521900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>480000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>303400</v>
+      </c>
+      <c r="E83" s="3">
         <v>315800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>416500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>401100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>501900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>516700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>365000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>295000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>120300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>45200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>25400</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q83" s="3">
         <v>33500</v>
       </c>
-      <c r="Q83" s="3" t="s">
+      <c r="R83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7254300</v>
+      </c>
+      <c r="E89" s="3">
         <v>5435900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4982600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4017500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3923900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3812200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2472600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1950600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1827200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2138600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1124300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>926500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>799900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>606100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>604500</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-152300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-174700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-324600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-304500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-252200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-161700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-173700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-315400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-254300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-156800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-120600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-84800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-33400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-25600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-60900</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4744000</v>
+      </c>
+      <c r="E94" s="3">
         <v>2454600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2403600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1068500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1114200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4471500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3179200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1973000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1975700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1637800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-353100</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-639100</v>
       </c>
-      <c r="Q94" s="3" t="s">
+      <c r="R94" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1976700</v>
+      </c>
+      <c r="E96" s="3">
         <v>1529700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1130200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>974800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>552300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>655600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1269700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>209400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>500700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-351600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-204300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-312800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-124600</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2882300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3745100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3027400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1484300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1981200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1518400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>155500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>230800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-200200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-310800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-227300</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q100" s="3" t="s">
+      <c r="R100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="E101" s="3">
         <v>1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-28600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>16000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>24800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>11900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>18300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>19800</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3" t="s">
+      <c r="R101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-426600</v>
+      </c>
+      <c r="E102" s="3">
         <v>4146800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-476900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1480600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>819700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>883900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-547000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>220300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-350600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>208300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>563800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>88800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-20200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-89500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>137900</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
